--- a/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -714,25 +714,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>76624500</v>
+        <v>77778500</v>
       </c>
       <c r="E8" s="3">
-        <v>65878800</v>
+        <v>66871000</v>
       </c>
       <c r="F8" s="3">
-        <v>59751100</v>
+        <v>60651000</v>
       </c>
       <c r="G8" s="3">
-        <v>54845600</v>
+        <v>55671600</v>
       </c>
       <c r="H8" s="3">
-        <v>57540200</v>
+        <v>58406700</v>
       </c>
       <c r="I8" s="3">
-        <v>56732000</v>
+        <v>57586400</v>
       </c>
       <c r="J8" s="3">
-        <v>50485600</v>
+        <v>51245900</v>
       </c>
       <c r="K8" s="3">
         <v>59577000</v>
@@ -747,25 +747,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>55768900</v>
+        <v>56608800</v>
       </c>
       <c r="E9" s="3">
-        <v>47939700</v>
+        <v>48661700</v>
       </c>
       <c r="F9" s="3">
-        <v>73803400</v>
+        <v>74914900</v>
       </c>
       <c r="G9" s="3">
-        <v>36027000</v>
+        <v>36569600</v>
       </c>
       <c r="H9" s="3">
-        <v>38392400</v>
+        <v>38970600</v>
       </c>
       <c r="I9" s="3">
-        <v>38325400</v>
+        <v>38902600</v>
       </c>
       <c r="J9" s="3">
-        <v>34632200</v>
+        <v>35153800</v>
       </c>
       <c r="K9" s="3">
         <v>41207500</v>
@@ -780,25 +780,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>20855600</v>
+        <v>21169700</v>
       </c>
       <c r="E10" s="3">
-        <v>17939100</v>
+        <v>18209300</v>
       </c>
       <c r="F10" s="3">
-        <v>-14052300</v>
+        <v>-14263900</v>
       </c>
       <c r="G10" s="3">
-        <v>18818600</v>
+        <v>19102000</v>
       </c>
       <c r="H10" s="3">
-        <v>19147700</v>
+        <v>19436100</v>
       </c>
       <c r="I10" s="3">
-        <v>18406600</v>
+        <v>18683800</v>
       </c>
       <c r="J10" s="3">
-        <v>15853300</v>
+        <v>16092100</v>
       </c>
       <c r="K10" s="3">
         <v>18369400</v>
@@ -834,19 +834,19 @@
         <v>8</v>
       </c>
       <c r="F12" s="3">
-        <v>3487200</v>
+        <v>3539700</v>
       </c>
       <c r="G12" s="3">
-        <v>3315300</v>
+        <v>3365200</v>
       </c>
       <c r="H12" s="3">
-        <v>3195200</v>
+        <v>3243300</v>
       </c>
       <c r="I12" s="3">
-        <v>3044600</v>
+        <v>3090400</v>
       </c>
       <c r="J12" s="3">
-        <v>2971100</v>
+        <v>3015900</v>
       </c>
       <c r="K12" s="3">
         <v>3441100</v>
@@ -900,19 +900,19 @@
         <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>158300</v>
+        <v>160600</v>
       </c>
       <c r="G14" s="3">
-        <v>197700</v>
+        <v>200700</v>
       </c>
       <c r="H14" s="3">
-        <v>311600</v>
+        <v>316300</v>
       </c>
       <c r="I14" s="3">
-        <v>256300</v>
+        <v>260200</v>
       </c>
       <c r="J14" s="3">
-        <v>744100</v>
+        <v>755300</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -972,25 +972,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>68602000</v>
+        <v>69635200</v>
       </c>
       <c r="E17" s="3">
-        <v>57895300</v>
+        <v>58767200</v>
       </c>
       <c r="F17" s="3">
-        <v>53408200</v>
+        <v>54212600</v>
       </c>
       <c r="G17" s="3">
-        <v>49231800</v>
+        <v>49973200</v>
       </c>
       <c r="H17" s="3">
-        <v>51602400</v>
+        <v>52379600</v>
       </c>
       <c r="I17" s="3">
-        <v>51852600</v>
+        <v>52633500</v>
       </c>
       <c r="J17" s="3">
-        <v>48568600</v>
+        <v>49300100</v>
       </c>
       <c r="K17" s="3">
         <v>57414600</v>
@@ -1005,25 +1005,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8022500</v>
+        <v>8143300</v>
       </c>
       <c r="E18" s="3">
-        <v>7983500</v>
+        <v>8103800</v>
       </c>
       <c r="F18" s="3">
-        <v>6342900</v>
+        <v>6438400</v>
       </c>
       <c r="G18" s="3">
-        <v>5613800</v>
+        <v>5698400</v>
       </c>
       <c r="H18" s="3">
-        <v>5937700</v>
+        <v>6027100</v>
       </c>
       <c r="I18" s="3">
-        <v>4879500</v>
+        <v>4953000</v>
       </c>
       <c r="J18" s="3">
-        <v>1917000</v>
+        <v>1945900</v>
       </c>
       <c r="K18" s="3">
         <v>2162300</v>
@@ -1053,25 +1053,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-9900</v>
+        <v>-10100</v>
       </c>
       <c r="E20" s="3">
-        <v>-466400</v>
+        <v>-473400</v>
       </c>
       <c r="F20" s="3">
-        <v>458800</v>
+        <v>465800</v>
       </c>
       <c r="G20" s="3">
-        <v>-231900</v>
+        <v>-235400</v>
       </c>
       <c r="H20" s="3">
-        <v>862400</v>
+        <v>875400</v>
       </c>
       <c r="I20" s="3">
-        <v>-147700</v>
+        <v>-149900</v>
       </c>
       <c r="J20" s="3">
-        <v>-149700</v>
+        <v>-151900</v>
       </c>
       <c r="K20" s="3">
         <v>261600</v>
@@ -1086,25 +1086,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>14652900</v>
+        <v>14934300</v>
       </c>
       <c r="E21" s="3">
-        <v>13038100</v>
+        <v>13284900</v>
       </c>
       <c r="F21" s="3">
-        <v>11345300</v>
+        <v>11557700</v>
       </c>
       <c r="G21" s="3">
-        <v>8136000</v>
+        <v>8283700</v>
       </c>
       <c r="H21" s="3">
-        <v>9272400</v>
+        <v>9434700</v>
       </c>
       <c r="I21" s="3">
-        <v>7120900</v>
+        <v>7250000</v>
       </c>
       <c r="J21" s="3">
-        <v>3929100</v>
+        <v>4008100</v>
       </c>
       <c r="K21" s="3">
         <v>5314800</v>
@@ -1119,25 +1119,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>175300</v>
+        <v>177900</v>
       </c>
       <c r="E22" s="3">
-        <v>96900</v>
+        <v>98400</v>
       </c>
       <c r="F22" s="3">
-        <v>175200</v>
+        <v>177900</v>
       </c>
       <c r="G22" s="3">
-        <v>73600</v>
+        <v>74700</v>
       </c>
       <c r="H22" s="3">
-        <v>82800</v>
+        <v>84000</v>
       </c>
       <c r="I22" s="3">
-        <v>90100</v>
+        <v>91400</v>
       </c>
       <c r="J22" s="3">
-        <v>96600</v>
+        <v>98000</v>
       </c>
       <c r="K22" s="3">
         <v>185900</v>
@@ -1152,25 +1152,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>7837300</v>
+        <v>7955300</v>
       </c>
       <c r="E23" s="3">
-        <v>7420200</v>
+        <v>7532000</v>
       </c>
       <c r="F23" s="3">
-        <v>6626500</v>
+        <v>6726300</v>
       </c>
       <c r="G23" s="3">
-        <v>5308300</v>
+        <v>5388300</v>
       </c>
       <c r="H23" s="3">
-        <v>6717300</v>
+        <v>6818500</v>
       </c>
       <c r="I23" s="3">
-        <v>4641700</v>
+        <v>4711600</v>
       </c>
       <c r="J23" s="3">
-        <v>1670800</v>
+        <v>1695900</v>
       </c>
       <c r="K23" s="3">
         <v>2238100</v>
@@ -1185,25 +1185,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1571600</v>
+        <v>1595300</v>
       </c>
       <c r="E24" s="3">
-        <v>1521200</v>
+        <v>1544100</v>
       </c>
       <c r="F24" s="3">
-        <v>-305000</v>
+        <v>-309600</v>
       </c>
       <c r="G24" s="3">
-        <v>1176500</v>
+        <v>1194300</v>
       </c>
       <c r="H24" s="3">
-        <v>299500</v>
+        <v>304000</v>
       </c>
       <c r="I24" s="3">
-        <v>1007800</v>
+        <v>1022900</v>
       </c>
       <c r="J24" s="3">
-        <v>823700</v>
+        <v>836200</v>
       </c>
       <c r="K24" s="3">
         <v>696700</v>
@@ -1251,25 +1251,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>6265700</v>
+        <v>6360000</v>
       </c>
       <c r="E26" s="3">
-        <v>5899000</v>
+        <v>5987900</v>
       </c>
       <c r="F26" s="3">
-        <v>6931500</v>
+        <v>7035900</v>
       </c>
       <c r="G26" s="3">
-        <v>4131800</v>
+        <v>4194000</v>
       </c>
       <c r="H26" s="3">
-        <v>6417900</v>
+        <v>6514500</v>
       </c>
       <c r="I26" s="3">
-        <v>3633900</v>
+        <v>3688700</v>
       </c>
       <c r="J26" s="3">
-        <v>847000</v>
+        <v>859800</v>
       </c>
       <c r="K26" s="3">
         <v>1541400</v>
@@ -1284,25 +1284,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6222500</v>
+        <v>6316200</v>
       </c>
       <c r="E27" s="3">
-        <v>5857700</v>
+        <v>5945900</v>
       </c>
       <c r="F27" s="3">
-        <v>6706500</v>
+        <v>6807500</v>
       </c>
       <c r="G27" s="3">
-        <v>3865700</v>
+        <v>3924000</v>
       </c>
       <c r="H27" s="3">
-        <v>6084000</v>
+        <v>6175700</v>
       </c>
       <c r="I27" s="3">
-        <v>3258900</v>
+        <v>3308000</v>
       </c>
       <c r="J27" s="3">
-        <v>486600</v>
+        <v>494000</v>
       </c>
       <c r="K27" s="3">
         <v>1086300</v>
@@ -1449,25 +1449,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>9900</v>
+        <v>10100</v>
       </c>
       <c r="E32" s="3">
-        <v>466400</v>
+        <v>473400</v>
       </c>
       <c r="F32" s="3">
-        <v>-458800</v>
+        <v>-465800</v>
       </c>
       <c r="G32" s="3">
-        <v>231900</v>
+        <v>235400</v>
       </c>
       <c r="H32" s="3">
-        <v>-862400</v>
+        <v>-875400</v>
       </c>
       <c r="I32" s="3">
-        <v>147700</v>
+        <v>149900</v>
       </c>
       <c r="J32" s="3">
-        <v>149700</v>
+        <v>151900</v>
       </c>
       <c r="K32" s="3">
         <v>-261600</v>
@@ -1482,25 +1482,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6222500</v>
+        <v>6316200</v>
       </c>
       <c r="E33" s="3">
-        <v>5857700</v>
+        <v>5945900</v>
       </c>
       <c r="F33" s="3">
-        <v>6706500</v>
+        <v>6807500</v>
       </c>
       <c r="G33" s="3">
-        <v>3865700</v>
+        <v>3924000</v>
       </c>
       <c r="H33" s="3">
-        <v>6084000</v>
+        <v>6175700</v>
       </c>
       <c r="I33" s="3">
-        <v>3258900</v>
+        <v>3308000</v>
       </c>
       <c r="J33" s="3">
-        <v>486600</v>
+        <v>494000</v>
       </c>
       <c r="K33" s="3">
         <v>1086300</v>
@@ -1548,25 +1548,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6222500</v>
+        <v>6316200</v>
       </c>
       <c r="E35" s="3">
-        <v>5857700</v>
+        <v>5945900</v>
       </c>
       <c r="F35" s="3">
-        <v>6706500</v>
+        <v>6807500</v>
       </c>
       <c r="G35" s="3">
-        <v>3865700</v>
+        <v>3924000</v>
       </c>
       <c r="H35" s="3">
-        <v>6084000</v>
+        <v>6175700</v>
       </c>
       <c r="I35" s="3">
-        <v>3258900</v>
+        <v>3308000</v>
       </c>
       <c r="J35" s="3">
-        <v>486600</v>
+        <v>494000</v>
       </c>
       <c r="K35" s="3">
         <v>1086300</v>
@@ -1649,25 +1649,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>9833200</v>
+        <v>9981300</v>
       </c>
       <c r="E41" s="3">
-        <v>13609600</v>
+        <v>13814500</v>
       </c>
       <c r="F41" s="3">
-        <v>23731100</v>
+        <v>24088500</v>
       </c>
       <c r="G41" s="3">
-        <v>10042100</v>
+        <v>10193300</v>
       </c>
       <c r="H41" s="3">
-        <v>9761300</v>
+        <v>9908300</v>
       </c>
       <c r="I41" s="3">
-        <v>10533200</v>
+        <v>10691900</v>
       </c>
       <c r="J41" s="3">
-        <v>6375300</v>
+        <v>6471400</v>
       </c>
       <c r="K41" s="3">
         <v>7229500</v>
@@ -1682,25 +1682,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2917000</v>
+        <v>2960900</v>
       </c>
       <c r="E42" s="3">
-        <v>3386200</v>
+        <v>3437200</v>
       </c>
       <c r="F42" s="3">
-        <v>22789200</v>
+        <v>23132400</v>
       </c>
       <c r="G42" s="3">
-        <v>12269200</v>
+        <v>12454000</v>
       </c>
       <c r="H42" s="3">
-        <v>8794900</v>
+        <v>8927400</v>
       </c>
       <c r="I42" s="3">
-        <v>7812600</v>
+        <v>7930300</v>
       </c>
       <c r="J42" s="3">
-        <v>6981600</v>
+        <v>7086700</v>
       </c>
       <c r="K42" s="3">
         <v>6956000</v>
@@ -1715,25 +1715,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11759100</v>
+        <v>11936200</v>
       </c>
       <c r="E43" s="3">
-        <v>10813400</v>
+        <v>10976200</v>
       </c>
       <c r="F43" s="3">
-        <v>18053400</v>
+        <v>18325300</v>
       </c>
       <c r="G43" s="3">
-        <v>7908400</v>
+        <v>8027500</v>
       </c>
       <c r="H43" s="3">
-        <v>8561800</v>
+        <v>8690700</v>
       </c>
       <c r="I43" s="3">
-        <v>7991100</v>
+        <v>8111500</v>
       </c>
       <c r="J43" s="3">
-        <v>7818200</v>
+        <v>7936000</v>
       </c>
       <c r="K43" s="3">
         <v>7788400</v>
@@ -1748,25 +1748,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>19495600</v>
+        <v>19789200</v>
       </c>
       <c r="E44" s="3">
-        <v>5803400</v>
+        <v>5890800</v>
       </c>
       <c r="F44" s="3">
-        <v>8455000</v>
+        <v>8582300</v>
       </c>
       <c r="G44" s="3">
-        <v>3917400</v>
+        <v>3976400</v>
       </c>
       <c r="H44" s="3">
-        <v>4337800</v>
+        <v>4403100</v>
       </c>
       <c r="I44" s="3">
-        <v>4601100</v>
+        <v>4670400</v>
       </c>
       <c r="J44" s="3">
-        <v>4255100</v>
+        <v>4319200</v>
       </c>
       <c r="K44" s="3">
         <v>5021100</v>
@@ -1781,25 +1781,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3740500</v>
+        <v>3796900</v>
       </c>
       <c r="E45" s="3">
-        <v>3141200</v>
+        <v>3188500</v>
       </c>
       <c r="F45" s="3">
-        <v>6206700</v>
+        <v>6300200</v>
       </c>
       <c r="G45" s="3">
-        <v>3944300</v>
+        <v>4003700</v>
       </c>
       <c r="H45" s="3">
-        <v>3381800</v>
+        <v>3432700</v>
       </c>
       <c r="I45" s="3">
-        <v>3431200</v>
+        <v>3482900</v>
       </c>
       <c r="J45" s="3">
-        <v>3491700</v>
+        <v>3544300</v>
       </c>
       <c r="K45" s="3">
         <v>3850800</v>
@@ -1814,25 +1814,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>37997600</v>
+        <v>38569900</v>
       </c>
       <c r="E46" s="3">
-        <v>36753800</v>
+        <v>37307300</v>
       </c>
       <c r="F46" s="3">
-        <v>31307700</v>
+        <v>31779200</v>
       </c>
       <c r="G46" s="3">
-        <v>38081400</v>
+        <v>38654900</v>
       </c>
       <c r="H46" s="3">
-        <v>34837500</v>
+        <v>35362200</v>
       </c>
       <c r="I46" s="3">
-        <v>34369300</v>
+        <v>34886900</v>
       </c>
       <c r="J46" s="3">
-        <v>28922000</v>
+        <v>29357600</v>
       </c>
       <c r="K46" s="3">
         <v>30845900</v>
@@ -1847,25 +1847,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>128785000</v>
+        <v>130725000</v>
       </c>
       <c r="E47" s="3">
-        <v>128882000</v>
+        <v>130823000</v>
       </c>
       <c r="F47" s="3">
-        <v>215676000</v>
+        <v>218925000</v>
       </c>
       <c r="G47" s="3">
-        <v>84554600</v>
+        <v>85828000</v>
       </c>
       <c r="H47" s="3">
-        <v>77851700</v>
+        <v>79024100</v>
       </c>
       <c r="I47" s="3">
-        <v>71420200</v>
+        <v>72495800</v>
       </c>
       <c r="J47" s="3">
-        <v>67142300</v>
+        <v>68153500</v>
       </c>
       <c r="K47" s="3">
         <v>67870500</v>
@@ -1880,25 +1880,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>24208500</v>
+        <v>24573100</v>
       </c>
       <c r="E48" s="3">
-        <v>10136900</v>
+        <v>10289600</v>
       </c>
       <c r="F48" s="3">
-        <v>7231900</v>
+        <v>7340900</v>
       </c>
       <c r="G48" s="3">
-        <v>8640300</v>
+        <v>8770500</v>
       </c>
       <c r="H48" s="3">
-        <v>5159600</v>
+        <v>5237300</v>
       </c>
       <c r="I48" s="3">
-        <v>4910100</v>
+        <v>4984000</v>
       </c>
       <c r="J48" s="3">
-        <v>5034400</v>
+        <v>5110300</v>
       </c>
       <c r="K48" s="3">
         <v>6033000</v>
@@ -1913,25 +1913,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>45163100</v>
+        <v>45843300</v>
       </c>
       <c r="E49" s="3">
-        <v>18227100</v>
+        <v>18501600</v>
       </c>
       <c r="F49" s="3">
-        <v>34810900</v>
+        <v>35335100</v>
       </c>
       <c r="G49" s="3">
-        <v>11222900</v>
+        <v>11391900</v>
       </c>
       <c r="H49" s="3">
-        <v>11198500</v>
+        <v>11367100</v>
       </c>
       <c r="I49" s="3">
-        <v>7022900</v>
+        <v>7128600</v>
       </c>
       <c r="J49" s="3">
-        <v>7348600</v>
+        <v>7459300</v>
       </c>
       <c r="K49" s="3">
         <v>8982000</v>
@@ -2012,25 +2012,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10247800</v>
+        <v>10402100</v>
       </c>
       <c r="E52" s="3">
-        <v>8394100</v>
+        <v>8520500</v>
       </c>
       <c r="F52" s="3">
-        <v>13783600</v>
+        <v>13991200</v>
       </c>
       <c r="G52" s="3">
-        <v>10482000</v>
+        <v>10639900</v>
       </c>
       <c r="H52" s="3">
-        <v>10270400</v>
+        <v>10425100</v>
       </c>
       <c r="I52" s="3">
-        <v>8872700</v>
+        <v>9006400</v>
       </c>
       <c r="J52" s="3">
-        <v>8818700</v>
+        <v>8951500</v>
       </c>
       <c r="K52" s="3">
         <v>8817900</v>
@@ -2078,25 +2078,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>206863000</v>
+        <v>209979000</v>
       </c>
       <c r="E54" s="3">
-        <v>202394000</v>
+        <v>205442000</v>
       </c>
       <c r="F54" s="3">
-        <v>182652000</v>
+        <v>185403000</v>
       </c>
       <c r="G54" s="3">
-        <v>152981000</v>
+        <v>155285000</v>
       </c>
       <c r="H54" s="3">
-        <v>139318000</v>
+        <v>141416000</v>
       </c>
       <c r="I54" s="3">
-        <v>126595000</v>
+        <v>128502000</v>
       </c>
       <c r="J54" s="3">
-        <v>117266000</v>
+        <v>119032000</v>
       </c>
       <c r="K54" s="3">
         <v>122549000</v>
@@ -2141,25 +2141,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12390900</v>
+        <v>12577500</v>
       </c>
       <c r="E57" s="3">
-        <v>12239100</v>
+        <v>12423500</v>
       </c>
       <c r="F57" s="3">
-        <v>26247700</v>
+        <v>26643000</v>
       </c>
       <c r="G57" s="3">
-        <v>13353100</v>
+        <v>13554200</v>
       </c>
       <c r="H57" s="3">
-        <v>14509500</v>
+        <v>14728100</v>
       </c>
       <c r="I57" s="3">
-        <v>13167000</v>
+        <v>13365300</v>
       </c>
       <c r="J57" s="3">
-        <v>12846100</v>
+        <v>13039600</v>
       </c>
       <c r="K57" s="3">
         <v>14097900</v>
@@ -2174,25 +2174,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>13963100</v>
+        <v>14173400</v>
       </c>
       <c r="E58" s="3">
-        <v>14262500</v>
+        <v>14477300</v>
       </c>
       <c r="F58" s="3">
-        <v>10218000</v>
+        <v>10371900</v>
       </c>
       <c r="G58" s="3">
-        <v>5577500</v>
+        <v>5661500</v>
       </c>
       <c r="H58" s="3">
-        <v>5252800</v>
+        <v>5331900</v>
       </c>
       <c r="I58" s="3">
-        <v>4791500</v>
+        <v>4863700</v>
       </c>
       <c r="J58" s="3">
-        <v>3440000</v>
+        <v>3491900</v>
       </c>
       <c r="K58" s="3">
         <v>2476500</v>
@@ -2207,25 +2207,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>35520200</v>
+        <v>36055200</v>
       </c>
       <c r="E59" s="3">
-        <v>31665800</v>
+        <v>32142700</v>
       </c>
       <c r="F59" s="3">
-        <v>37950600</v>
+        <v>38522200</v>
       </c>
       <c r="G59" s="3">
-        <v>22506000</v>
+        <v>22844900</v>
       </c>
       <c r="H59" s="3">
-        <v>20607700</v>
+        <v>20918000</v>
       </c>
       <c r="I59" s="3">
-        <v>19361900</v>
+        <v>19653500</v>
       </c>
       <c r="J59" s="3">
-        <v>18386200</v>
+        <v>18663100</v>
       </c>
       <c r="K59" s="3">
         <v>18931600</v>
@@ -2240,25 +2240,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>61874200</v>
+        <v>62806100</v>
       </c>
       <c r="E60" s="3">
-        <v>58167400</v>
+        <v>59043400</v>
       </c>
       <c r="F60" s="3">
-        <v>48827900</v>
+        <v>49563300</v>
       </c>
       <c r="G60" s="3">
-        <v>41436500</v>
+        <v>42060600</v>
       </c>
       <c r="H60" s="3">
-        <v>40370000</v>
+        <v>40978000</v>
       </c>
       <c r="I60" s="3">
-        <v>37320400</v>
+        <v>37882400</v>
       </c>
       <c r="J60" s="3">
-        <v>34672300</v>
+        <v>35194500</v>
       </c>
       <c r="K60" s="3">
         <v>35506000</v>
@@ -2273,25 +2273,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11737500</v>
+        <v>11914300</v>
       </c>
       <c r="E61" s="3">
-        <v>7992200</v>
+        <v>8112600</v>
       </c>
       <c r="F61" s="3">
-        <v>6996100</v>
+        <v>7101500</v>
       </c>
       <c r="G61" s="3">
-        <v>4216200</v>
+        <v>4279700</v>
       </c>
       <c r="H61" s="3">
-        <v>3774000</v>
+        <v>3830800</v>
       </c>
       <c r="I61" s="3">
-        <v>4139700</v>
+        <v>4202100</v>
       </c>
       <c r="J61" s="3">
-        <v>4524900</v>
+        <v>4593100</v>
       </c>
       <c r="K61" s="3">
         <v>4091000</v>
@@ -2306,25 +2306,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>171470000</v>
+        <v>174053000</v>
       </c>
       <c r="E62" s="3">
-        <v>88444300</v>
+        <v>89776300</v>
       </c>
       <c r="F62" s="3">
-        <v>90182400</v>
+        <v>91540600</v>
       </c>
       <c r="G62" s="3">
-        <v>75474400</v>
+        <v>76611100</v>
       </c>
       <c r="H62" s="3">
-        <v>65655700</v>
+        <v>66644500</v>
       </c>
       <c r="I62" s="3">
-        <v>60856800</v>
+        <v>61773300</v>
       </c>
       <c r="J62" s="3">
-        <v>57169600</v>
+        <v>58030600</v>
       </c>
       <c r="K62" s="3">
         <v>59933000</v>
@@ -2438,25 +2438,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>163049000</v>
+        <v>165505000</v>
       </c>
       <c r="E66" s="3">
-        <v>154954000</v>
+        <v>157288000</v>
       </c>
       <c r="F66" s="3">
-        <v>138295000</v>
+        <v>140377000</v>
       </c>
       <c r="G66" s="3">
-        <v>125589000</v>
+        <v>127481000</v>
       </c>
       <c r="H66" s="3">
-        <v>114442000</v>
+        <v>116165000</v>
       </c>
       <c r="I66" s="3">
-        <v>106892000</v>
+        <v>108502000</v>
       </c>
       <c r="J66" s="3">
-        <v>100684000</v>
+        <v>102201000</v>
       </c>
       <c r="K66" s="3">
         <v>104444000</v>
@@ -2618,25 +2618,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>33813800</v>
+        <v>34323100</v>
       </c>
       <c r="E72" s="3">
-        <v>24971500</v>
+        <v>25347500</v>
       </c>
       <c r="F72" s="3">
-        <v>19352300</v>
+        <v>19643800</v>
       </c>
       <c r="G72" s="3">
-        <v>18385200</v>
+        <v>18662100</v>
       </c>
       <c r="H72" s="3">
-        <v>15408700</v>
+        <v>15640700</v>
       </c>
       <c r="I72" s="3">
-        <v>9564200</v>
+        <v>9708200</v>
       </c>
       <c r="J72" s="3">
-        <v>6536200</v>
+        <v>6634600</v>
       </c>
       <c r="K72" s="3">
         <v>6882000</v>
@@ -2750,25 +2750,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>43814300</v>
+        <v>44474100</v>
       </c>
       <c r="E76" s="3">
-        <v>47439300</v>
+        <v>48153700</v>
       </c>
       <c r="F76" s="3">
-        <v>44357500</v>
+        <v>45025500</v>
       </c>
       <c r="G76" s="3">
-        <v>27392000</v>
+        <v>27804600</v>
       </c>
       <c r="H76" s="3">
-        <v>24875900</v>
+        <v>25250600</v>
       </c>
       <c r="I76" s="3">
-        <v>19703300</v>
+        <v>20000000</v>
       </c>
       <c r="J76" s="3">
-        <v>16581700</v>
+        <v>16831400</v>
       </c>
       <c r="K76" s="3">
         <v>18105500</v>
@@ -2854,25 +2854,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6222500</v>
+        <v>6316200</v>
       </c>
       <c r="E81" s="3">
-        <v>5857700</v>
+        <v>5945900</v>
       </c>
       <c r="F81" s="3">
-        <v>6706500</v>
+        <v>6807500</v>
       </c>
       <c r="G81" s="3">
-        <v>3865700</v>
+        <v>3924000</v>
       </c>
       <c r="H81" s="3">
-        <v>6084000</v>
+        <v>6175700</v>
       </c>
       <c r="I81" s="3">
-        <v>3258900</v>
+        <v>3308000</v>
       </c>
       <c r="J81" s="3">
-        <v>486600</v>
+        <v>494000</v>
       </c>
       <c r="K81" s="3">
         <v>1086300</v>
@@ -2902,25 +2902,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6670500</v>
+        <v>6770900</v>
       </c>
       <c r="E83" s="3">
-        <v>5545900</v>
+        <v>5629500</v>
       </c>
       <c r="F83" s="3">
-        <v>4564200</v>
+        <v>4632900</v>
       </c>
       <c r="G83" s="3">
-        <v>2766500</v>
+        <v>2808200</v>
       </c>
       <c r="H83" s="3">
-        <v>2483500</v>
+        <v>2520900</v>
       </c>
       <c r="I83" s="3">
-        <v>2400000</v>
+        <v>2436100</v>
       </c>
       <c r="J83" s="3">
-        <v>2171600</v>
+        <v>2204300</v>
       </c>
       <c r="K83" s="3">
         <v>2918600</v>
@@ -3100,25 +3100,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2089500</v>
+        <v>2121000</v>
       </c>
       <c r="E89" s="3">
-        <v>8191400</v>
+        <v>8314800</v>
       </c>
       <c r="F89" s="3">
-        <v>7571000</v>
+        <v>7685100</v>
       </c>
       <c r="G89" s="3">
-        <v>8942800</v>
+        <v>9077500</v>
       </c>
       <c r="H89" s="3">
-        <v>8333200</v>
+        <v>8458700</v>
       </c>
       <c r="I89" s="3">
-        <v>8282500</v>
+        <v>8407200</v>
       </c>
       <c r="J89" s="3">
-        <v>5373500</v>
+        <v>5454400</v>
       </c>
       <c r="K89" s="3">
         <v>5505800</v>
@@ -3148,25 +3148,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4074500</v>
+        <v>-4135900</v>
       </c>
       <c r="E91" s="3">
-        <v>-2928900</v>
+        <v>-2973000</v>
       </c>
       <c r="F91" s="3">
-        <v>-6574700</v>
+        <v>-6673700</v>
       </c>
       <c r="G91" s="3">
-        <v>-2920000</v>
+        <v>-2964000</v>
       </c>
       <c r="H91" s="3">
-        <v>-2076000</v>
+        <v>-2107200</v>
       </c>
       <c r="I91" s="3">
-        <v>-1746200</v>
+        <v>-1772500</v>
       </c>
       <c r="J91" s="3">
-        <v>-2214500</v>
+        <v>-2247900</v>
       </c>
       <c r="K91" s="3">
         <v>-2759300</v>
@@ -3247,25 +3247,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6989700</v>
+        <v>-7095000</v>
       </c>
       <c r="E94" s="3">
-        <v>-4839100</v>
+        <v>-4912000</v>
       </c>
       <c r="F94" s="3">
-        <v>-3744400</v>
+        <v>-3800800</v>
       </c>
       <c r="G94" s="3">
-        <v>-8979100</v>
+        <v>-9114400</v>
       </c>
       <c r="H94" s="3">
-        <v>-8681400</v>
+        <v>-8812200</v>
       </c>
       <c r="I94" s="3">
-        <v>-5465200</v>
+        <v>-5547500</v>
       </c>
       <c r="J94" s="3">
-        <v>-8326400</v>
+        <v>-8451800</v>
       </c>
       <c r="K94" s="3">
         <v>-7573500</v>
@@ -3295,25 +3295,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-574800</v>
+        <v>-583500</v>
       </c>
       <c r="E96" s="3">
-        <v>-493600</v>
+        <v>-501100</v>
       </c>
       <c r="F96" s="3">
-        <v>-407000</v>
+        <v>-413100</v>
       </c>
       <c r="G96" s="3">
-        <v>-329200</v>
+        <v>-334100</v>
       </c>
       <c r="H96" s="3">
-        <v>-252800</v>
+        <v>-256600</v>
       </c>
       <c r="I96" s="3">
-        <v>-189200</v>
+        <v>-192000</v>
       </c>
       <c r="J96" s="3">
-        <v>-168000</v>
+        <v>-170500</v>
       </c>
       <c r="K96" s="3">
         <v>-93700</v>
@@ -3427,25 +3427,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>559800</v>
+        <v>568200</v>
       </c>
       <c r="E100" s="3">
-        <v>-2234900</v>
+        <v>-2268500</v>
       </c>
       <c r="F100" s="3">
-        <v>-2247900</v>
+        <v>-2281700</v>
       </c>
       <c r="G100" s="3">
-        <v>436000</v>
+        <v>442500</v>
       </c>
       <c r="H100" s="3">
-        <v>-815900</v>
+        <v>-828200</v>
       </c>
       <c r="I100" s="3">
-        <v>1636500</v>
+        <v>1661100</v>
       </c>
       <c r="J100" s="3">
-        <v>3003300</v>
+        <v>3048500</v>
       </c>
       <c r="K100" s="3">
         <v>2793900</v>
@@ -3460,25 +3460,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>564000</v>
+        <v>572500</v>
       </c>
       <c r="E101" s="3">
-        <v>626600</v>
+        <v>636000</v>
       </c>
       <c r="F101" s="3">
-        <v>243600</v>
+        <v>247300</v>
       </c>
       <c r="G101" s="3">
-        <v>-143700</v>
+        <v>-145900</v>
       </c>
       <c r="H101" s="3">
-        <v>348400</v>
+        <v>353600</v>
       </c>
       <c r="I101" s="3">
-        <v>-352200</v>
+        <v>-357500</v>
       </c>
       <c r="J101" s="3">
-        <v>-206200</v>
+        <v>-209400</v>
       </c>
       <c r="K101" s="3">
         <v>-474900</v>
@@ -3493,25 +3493,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3776400</v>
+        <v>-3833300</v>
       </c>
       <c r="E102" s="3">
-        <v>1744000</v>
+        <v>1770300</v>
       </c>
       <c r="F102" s="3">
-        <v>1822400</v>
+        <v>1849900</v>
       </c>
       <c r="G102" s="3">
-        <v>255900</v>
+        <v>259800</v>
       </c>
       <c r="H102" s="3">
-        <v>-815800</v>
+        <v>-828100</v>
       </c>
       <c r="I102" s="3">
-        <v>4101600</v>
+        <v>4163300</v>
       </c>
       <c r="J102" s="3">
-        <v>-155800</v>
+        <v>-158200</v>
       </c>
       <c r="K102" s="3">
         <v>251400</v>

--- a/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
   <si>
     <t>SONY</t>
   </si>
@@ -656,159 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>77778500</v>
+        <v>83072500</v>
       </c>
       <c r="E8" s="3">
-        <v>66871000</v>
+        <v>70016500</v>
       </c>
       <c r="F8" s="3">
-        <v>60651000</v>
+        <v>63299300</v>
       </c>
       <c r="G8" s="3">
-        <v>55671600</v>
+        <v>57411500</v>
       </c>
       <c r="H8" s="3">
-        <v>58406700</v>
+        <v>52698100</v>
       </c>
       <c r="I8" s="3">
-        <v>57586400</v>
+        <v>55287100</v>
       </c>
       <c r="J8" s="3">
+        <v>54510600</v>
+      </c>
+      <c r="K8" s="3">
         <v>51245900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>59577000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>70081500</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>56608800</v>
+        <v>52691000</v>
       </c>
       <c r="E9" s="3">
-        <v>48661700</v>
+        <v>54203700</v>
       </c>
       <c r="F9" s="3">
-        <v>74914900</v>
+        <v>46062600</v>
       </c>
       <c r="G9" s="3">
-        <v>36569600</v>
+        <v>70913500</v>
       </c>
       <c r="H9" s="3">
-        <v>38970600</v>
+        <v>34616300</v>
       </c>
       <c r="I9" s="3">
-        <v>38902600</v>
+        <v>36889100</v>
       </c>
       <c r="J9" s="3">
+        <v>36824700</v>
+      </c>
+      <c r="K9" s="3">
         <v>35153800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>41207500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>48568200</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>21169700</v>
+        <v>30381500</v>
       </c>
       <c r="E10" s="3">
-        <v>18209300</v>
+        <v>15812800</v>
       </c>
       <c r="F10" s="3">
-        <v>-14263900</v>
+        <v>17236700</v>
       </c>
       <c r="G10" s="3">
-        <v>19102000</v>
+        <v>-13502100</v>
       </c>
       <c r="H10" s="3">
-        <v>19436100</v>
+        <v>18081700</v>
       </c>
       <c r="I10" s="3">
-        <v>18683800</v>
+        <v>18398000</v>
       </c>
       <c r="J10" s="3">
+        <v>17685900</v>
+      </c>
+      <c r="K10" s="3">
         <v>16092100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18369400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>21513200</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +834,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -833,30 +846,33 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
-        <v>3539700</v>
+      <c r="F12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G12" s="3">
-        <v>3365200</v>
+        <v>3350600</v>
       </c>
       <c r="H12" s="3">
-        <v>3243300</v>
+        <v>3185500</v>
       </c>
       <c r="I12" s="3">
-        <v>3090400</v>
+        <v>3070100</v>
       </c>
       <c r="J12" s="3">
+        <v>2925300</v>
+      </c>
+      <c r="K12" s="3">
         <v>3015900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3441100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3960600</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,9 +903,12 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -899,30 +918,33 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>160600</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>200700</v>
+        <v>152100</v>
       </c>
       <c r="H14" s="3">
-        <v>316300</v>
+        <v>190000</v>
       </c>
       <c r="I14" s="3">
-        <v>260200</v>
+        <v>299400</v>
       </c>
       <c r="J14" s="3">
+        <v>246300</v>
+      </c>
+      <c r="K14" s="3">
         <v>755300</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -953,9 +975,12 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -966,74 +991,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>69635200</v>
+        <v>75360200</v>
       </c>
       <c r="E17" s="3">
-        <v>58767200</v>
+        <v>61707300</v>
       </c>
       <c r="F17" s="3">
-        <v>54212600</v>
+        <v>55628300</v>
       </c>
       <c r="G17" s="3">
-        <v>49973200</v>
+        <v>51316900</v>
       </c>
       <c r="H17" s="3">
-        <v>52379600</v>
+        <v>47304000</v>
       </c>
       <c r="I17" s="3">
-        <v>52633500</v>
+        <v>49581900</v>
       </c>
       <c r="J17" s="3">
+        <v>49822200</v>
+      </c>
+      <c r="K17" s="3">
         <v>49300100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>57414600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>69496700</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8143300</v>
+        <v>7712300</v>
       </c>
       <c r="E18" s="3">
-        <v>8103800</v>
+        <v>8309200</v>
       </c>
       <c r="F18" s="3">
-        <v>6438400</v>
+        <v>7670900</v>
       </c>
       <c r="G18" s="3">
-        <v>5698400</v>
+        <v>6094500</v>
       </c>
       <c r="H18" s="3">
-        <v>6027100</v>
+        <v>5394000</v>
       </c>
       <c r="I18" s="3">
-        <v>4953000</v>
+        <v>5705200</v>
       </c>
       <c r="J18" s="3">
+        <v>4688400</v>
+      </c>
+      <c r="K18" s="3">
         <v>1945900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2162300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>584700</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1047,173 +1079,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-10100</v>
+        <v>381700</v>
       </c>
       <c r="E20" s="3">
-        <v>-473400</v>
+        <v>-9500</v>
       </c>
       <c r="F20" s="3">
-        <v>465800</v>
+        <v>-448100</v>
       </c>
       <c r="G20" s="3">
-        <v>-235400</v>
+        <v>440900</v>
       </c>
       <c r="H20" s="3">
-        <v>875400</v>
+        <v>-222800</v>
       </c>
       <c r="I20" s="3">
-        <v>-149900</v>
+        <v>828600</v>
       </c>
       <c r="J20" s="3">
+        <v>-141900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-151900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>261600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-44500</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>14934300</v>
+        <v>15387600</v>
       </c>
       <c r="E21" s="3">
-        <v>13284900</v>
+        <v>14698900</v>
       </c>
       <c r="F21" s="3">
-        <v>11557700</v>
+        <v>12543300</v>
       </c>
       <c r="G21" s="3">
-        <v>8283700</v>
+        <v>10914000</v>
       </c>
       <c r="H21" s="3">
-        <v>9434700</v>
+        <v>7825300</v>
       </c>
       <c r="I21" s="3">
-        <v>7250000</v>
+        <v>8916400</v>
       </c>
       <c r="J21" s="3">
+        <v>6848900</v>
+      </c>
+      <c r="K21" s="3">
         <v>4008100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5314800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3600600</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>177900</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>98400</v>
+        <v>168400</v>
       </c>
       <c r="F22" s="3">
-        <v>177900</v>
+        <v>93100</v>
       </c>
       <c r="G22" s="3">
-        <v>74700</v>
+        <v>168400</v>
       </c>
       <c r="H22" s="3">
-        <v>84000</v>
+        <v>70800</v>
       </c>
       <c r="I22" s="3">
-        <v>91400</v>
+        <v>79500</v>
       </c>
       <c r="J22" s="3">
+        <v>86600</v>
+      </c>
+      <c r="K22" s="3">
         <v>98000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>185900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>201300</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>7955300</v>
+        <v>8094100</v>
       </c>
       <c r="E23" s="3">
-        <v>7532000</v>
+        <v>8131300</v>
       </c>
       <c r="F23" s="3">
-        <v>6726300</v>
+        <v>7129700</v>
       </c>
       <c r="G23" s="3">
-        <v>5388300</v>
+        <v>6367000</v>
       </c>
       <c r="H23" s="3">
-        <v>6818500</v>
+        <v>5100500</v>
       </c>
       <c r="I23" s="3">
-        <v>4711600</v>
+        <v>6454300</v>
       </c>
       <c r="J23" s="3">
+        <v>4459900</v>
+      </c>
+      <c r="K23" s="3">
         <v>1695900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2238100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>338900</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1595300</v>
+        <v>1838500</v>
       </c>
       <c r="E24" s="3">
-        <v>1544100</v>
+        <v>1676200</v>
       </c>
       <c r="F24" s="3">
-        <v>-309600</v>
+        <v>1461600</v>
       </c>
       <c r="G24" s="3">
-        <v>1194300</v>
+        <v>-293000</v>
       </c>
       <c r="H24" s="3">
-        <v>304000</v>
+        <v>1130500</v>
       </c>
       <c r="I24" s="3">
-        <v>1022900</v>
+        <v>287700</v>
       </c>
       <c r="J24" s="3">
+        <v>968300</v>
+      </c>
+      <c r="K24" s="3">
         <v>836200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>696700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>756900</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1244,75 +1292,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>6360000</v>
+        <v>6255600</v>
       </c>
       <c r="E26" s="3">
-        <v>5987900</v>
+        <v>6455100</v>
       </c>
       <c r="F26" s="3">
-        <v>7035900</v>
+        <v>5668000</v>
       </c>
       <c r="G26" s="3">
-        <v>4194000</v>
+        <v>6660100</v>
       </c>
       <c r="H26" s="3">
-        <v>6514500</v>
+        <v>3970000</v>
       </c>
       <c r="I26" s="3">
-        <v>3688700</v>
+        <v>6166600</v>
       </c>
       <c r="J26" s="3">
+        <v>3491600</v>
+      </c>
+      <c r="K26" s="3">
         <v>859800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1541400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-418000</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6316200</v>
+        <v>6192300</v>
       </c>
       <c r="E27" s="3">
-        <v>5945900</v>
+        <v>6413700</v>
       </c>
       <c r="F27" s="3">
-        <v>6807500</v>
+        <v>5628300</v>
       </c>
       <c r="G27" s="3">
-        <v>3924000</v>
+        <v>6443900</v>
       </c>
       <c r="H27" s="3">
-        <v>6175700</v>
+        <v>3714400</v>
       </c>
       <c r="I27" s="3">
-        <v>3308000</v>
+        <v>5845800</v>
       </c>
       <c r="J27" s="3">
+        <v>3131300</v>
+      </c>
+      <c r="K27" s="3">
         <v>494000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1086300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1074600</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1343,9 +1400,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1376,9 +1436,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1409,9 +1472,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1442,75 +1508,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>10100</v>
+        <v>-381700</v>
       </c>
       <c r="E32" s="3">
-        <v>473400</v>
+        <v>9500</v>
       </c>
       <c r="F32" s="3">
-        <v>-465800</v>
+        <v>448100</v>
       </c>
       <c r="G32" s="3">
-        <v>235400</v>
+        <v>-440900</v>
       </c>
       <c r="H32" s="3">
-        <v>-875400</v>
+        <v>222800</v>
       </c>
       <c r="I32" s="3">
-        <v>149900</v>
+        <v>-828600</v>
       </c>
       <c r="J32" s="3">
+        <v>141900</v>
+      </c>
+      <c r="K32" s="3">
         <v>151900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-261600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>44500</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6316200</v>
+        <v>6192300</v>
       </c>
       <c r="E33" s="3">
-        <v>5945900</v>
+        <v>6413700</v>
       </c>
       <c r="F33" s="3">
-        <v>6807500</v>
+        <v>5628300</v>
       </c>
       <c r="G33" s="3">
-        <v>3924000</v>
+        <v>6443900</v>
       </c>
       <c r="H33" s="3">
-        <v>6175700</v>
+        <v>3714400</v>
       </c>
       <c r="I33" s="3">
-        <v>3308000</v>
+        <v>5845800</v>
       </c>
       <c r="J33" s="3">
+        <v>3131300</v>
+      </c>
+      <c r="K33" s="3">
         <v>494000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1086300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1074600</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1541,80 +1616,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6316200</v>
+        <v>6192300</v>
       </c>
       <c r="E35" s="3">
-        <v>5945900</v>
+        <v>6413700</v>
       </c>
       <c r="F35" s="3">
-        <v>6807500</v>
+        <v>5628300</v>
       </c>
       <c r="G35" s="3">
-        <v>3924000</v>
+        <v>6443900</v>
       </c>
       <c r="H35" s="3">
-        <v>6175700</v>
+        <v>3714400</v>
       </c>
       <c r="I35" s="3">
-        <v>3308000</v>
+        <v>5845800</v>
       </c>
       <c r="J35" s="3">
+        <v>3131300</v>
+      </c>
+      <c r="K35" s="3">
         <v>494000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1086300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1074600</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1712,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1643,305 +1728,333 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>9981300</v>
+        <v>12167400</v>
       </c>
       <c r="E41" s="3">
-        <v>13814500</v>
+        <v>9448100</v>
       </c>
       <c r="F41" s="3">
-        <v>24088500</v>
+        <v>13076700</v>
       </c>
       <c r="G41" s="3">
-        <v>10193300</v>
+        <v>22801900</v>
       </c>
       <c r="H41" s="3">
-        <v>9908300</v>
+        <v>9648800</v>
       </c>
       <c r="I41" s="3">
-        <v>10691900</v>
+        <v>9379100</v>
       </c>
       <c r="J41" s="3">
+        <v>10120800</v>
+      </c>
+      <c r="K41" s="3">
         <v>6471400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7229500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8098500</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>2960900</v>
+        <v>3340000</v>
       </c>
       <c r="E42" s="3">
-        <v>3437200</v>
+        <v>2802800</v>
       </c>
       <c r="F42" s="3">
-        <v>23132400</v>
+        <v>3253600</v>
       </c>
       <c r="G42" s="3">
-        <v>12454000</v>
+        <v>21896800</v>
       </c>
       <c r="H42" s="3">
-        <v>8927400</v>
+        <v>11788800</v>
       </c>
       <c r="I42" s="3">
-        <v>7930300</v>
+        <v>8450600</v>
       </c>
       <c r="J42" s="3">
+        <v>7506700</v>
+      </c>
+      <c r="K42" s="3">
         <v>7086700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6956000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7990300</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11936200</v>
+        <v>13769300</v>
       </c>
       <c r="E43" s="3">
-        <v>10976200</v>
+        <v>11298600</v>
       </c>
       <c r="F43" s="3">
-        <v>18325300</v>
+        <v>10390000</v>
       </c>
       <c r="G43" s="3">
-        <v>8027500</v>
+        <v>17346500</v>
       </c>
       <c r="H43" s="3">
-        <v>8690700</v>
+        <v>7598700</v>
       </c>
       <c r="I43" s="3">
-        <v>8111500</v>
+        <v>8226500</v>
       </c>
       <c r="J43" s="3">
+        <v>7678200</v>
+      </c>
+      <c r="K43" s="3">
         <v>7936000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7788400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9654700</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>19789200</v>
+        <v>9688900</v>
       </c>
       <c r="E44" s="3">
-        <v>5890800</v>
+        <v>18732200</v>
       </c>
       <c r="F44" s="3">
-        <v>8582300</v>
+        <v>5576200</v>
       </c>
       <c r="G44" s="3">
-        <v>3976400</v>
+        <v>8123900</v>
       </c>
       <c r="H44" s="3">
-        <v>4403100</v>
+        <v>3764000</v>
       </c>
       <c r="I44" s="3">
-        <v>4670400</v>
+        <v>4167900</v>
       </c>
       <c r="J44" s="3">
+        <v>4420900</v>
+      </c>
+      <c r="K44" s="3">
         <v>4319200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5021100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5676100</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3796900</v>
+        <v>4270400</v>
       </c>
       <c r="E45" s="3">
-        <v>3188500</v>
+        <v>3594100</v>
       </c>
       <c r="F45" s="3">
-        <v>6300200</v>
+        <v>3018200</v>
       </c>
       <c r="G45" s="3">
-        <v>4003700</v>
+        <v>5963700</v>
       </c>
       <c r="H45" s="3">
-        <v>3432700</v>
+        <v>3789900</v>
       </c>
       <c r="I45" s="3">
-        <v>3482900</v>
+        <v>3249300</v>
       </c>
       <c r="J45" s="3">
+        <v>3296800</v>
+      </c>
+      <c r="K45" s="3">
         <v>3544300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3850800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4388500</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>38569900</v>
+        <v>43236000</v>
       </c>
       <c r="E46" s="3">
-        <v>37307300</v>
+        <v>36509800</v>
       </c>
       <c r="F46" s="3">
-        <v>31779200</v>
+        <v>35314600</v>
       </c>
       <c r="G46" s="3">
-        <v>38654900</v>
+        <v>30081800</v>
       </c>
       <c r="H46" s="3">
-        <v>35362200</v>
+        <v>36590200</v>
       </c>
       <c r="I46" s="3">
-        <v>34886900</v>
+        <v>33473400</v>
       </c>
       <c r="J46" s="3">
+        <v>33023500</v>
+      </c>
+      <c r="K46" s="3">
         <v>29357600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>30845900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35808100</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>130725000</v>
+        <v>129264000</v>
       </c>
       <c r="E47" s="3">
-        <v>130823000</v>
+        <v>123742000</v>
       </c>
       <c r="F47" s="3">
-        <v>218925000</v>
+        <v>123835000</v>
       </c>
       <c r="G47" s="3">
-        <v>85828000</v>
+        <v>207231000</v>
       </c>
       <c r="H47" s="3">
-        <v>79024100</v>
+        <v>81243800</v>
       </c>
       <c r="I47" s="3">
-        <v>72495800</v>
+        <v>74803300</v>
       </c>
       <c r="J47" s="3">
+        <v>68623700</v>
+      </c>
+      <c r="K47" s="3">
         <v>68153500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>67870500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>72772400</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>24573100</v>
+        <v>12926100</v>
       </c>
       <c r="E48" s="3">
-        <v>10289600</v>
+        <v>23260500</v>
       </c>
       <c r="F48" s="3">
-        <v>7340900</v>
+        <v>9740000</v>
       </c>
       <c r="G48" s="3">
-        <v>8770500</v>
+        <v>6948800</v>
       </c>
       <c r="H48" s="3">
-        <v>5237300</v>
+        <v>8302000</v>
       </c>
       <c r="I48" s="3">
-        <v>4984000</v>
+        <v>4957600</v>
       </c>
       <c r="J48" s="3">
+        <v>4717800</v>
+      </c>
+      <c r="K48" s="3">
         <v>5110300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6033000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6306100</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>45843300</v>
+        <v>25716600</v>
       </c>
       <c r="E49" s="3">
-        <v>18501600</v>
+        <v>43394700</v>
       </c>
       <c r="F49" s="3">
-        <v>35335100</v>
+        <v>17513400</v>
       </c>
       <c r="G49" s="3">
-        <v>11391900</v>
+        <v>33447800</v>
       </c>
       <c r="H49" s="3">
-        <v>11367100</v>
+        <v>10783500</v>
       </c>
       <c r="I49" s="3">
-        <v>7128600</v>
+        <v>10760000</v>
       </c>
       <c r="J49" s="3">
+        <v>6747900</v>
+      </c>
+      <c r="K49" s="3">
         <v>7459300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8982000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10266800</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1972,9 +2085,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2005,42 +2121,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10402100</v>
+        <v>6462700</v>
       </c>
       <c r="E52" s="3">
-        <v>8520500</v>
+        <v>9846500</v>
       </c>
       <c r="F52" s="3">
-        <v>13991200</v>
+        <v>8065400</v>
       </c>
       <c r="G52" s="3">
-        <v>10639900</v>
+        <v>13243900</v>
       </c>
       <c r="H52" s="3">
-        <v>10425100</v>
+        <v>10071600</v>
       </c>
       <c r="I52" s="3">
-        <v>9006400</v>
+        <v>9868300</v>
       </c>
       <c r="J52" s="3">
+        <v>8525300</v>
+      </c>
+      <c r="K52" s="3">
         <v>8951500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8817900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9913400</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2071,42 +2193,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>209979000</v>
+        <v>217606000</v>
       </c>
       <c r="E54" s="3">
-        <v>205442000</v>
+        <v>198763000</v>
       </c>
       <c r="F54" s="3">
-        <v>185403000</v>
+        <v>194469000</v>
       </c>
       <c r="G54" s="3">
-        <v>155285000</v>
+        <v>175500000</v>
       </c>
       <c r="H54" s="3">
-        <v>141416000</v>
+        <v>146991000</v>
       </c>
       <c r="I54" s="3">
-        <v>128502000</v>
+        <v>133863000</v>
       </c>
       <c r="J54" s="3">
+        <v>121638000</v>
+      </c>
+      <c r="K54" s="3">
         <v>119032000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>122549000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>135067000</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2120,8 +2248,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2135,206 +2264,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12577500</v>
+        <v>13174100</v>
       </c>
       <c r="E57" s="3">
-        <v>12423500</v>
+        <v>11905700</v>
       </c>
       <c r="F57" s="3">
-        <v>26643000</v>
+        <v>11759900</v>
       </c>
       <c r="G57" s="3">
-        <v>13554200</v>
+        <v>25219900</v>
       </c>
       <c r="H57" s="3">
-        <v>14728100</v>
+        <v>12830200</v>
       </c>
       <c r="I57" s="3">
-        <v>13365300</v>
+        <v>13941400</v>
       </c>
       <c r="J57" s="3">
+        <v>12651400</v>
+      </c>
+      <c r="K57" s="3">
         <v>13039600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14097900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17028600</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14173400</v>
+        <v>12953400</v>
       </c>
       <c r="E58" s="3">
-        <v>14477300</v>
+        <v>13416300</v>
       </c>
       <c r="F58" s="3">
-        <v>10371900</v>
+        <v>13704000</v>
       </c>
       <c r="G58" s="3">
-        <v>5661500</v>
+        <v>9817900</v>
       </c>
       <c r="H58" s="3">
-        <v>5331900</v>
+        <v>5359100</v>
       </c>
       <c r="I58" s="3">
-        <v>4863700</v>
+        <v>5047100</v>
       </c>
       <c r="J58" s="3">
+        <v>4603900</v>
+      </c>
+      <c r="K58" s="3">
         <v>3491900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2476500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1889600</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>36055200</v>
+        <v>38897700</v>
       </c>
       <c r="E59" s="3">
-        <v>32142700</v>
+        <v>34129400</v>
       </c>
       <c r="F59" s="3">
-        <v>38522200</v>
+        <v>30425900</v>
       </c>
       <c r="G59" s="3">
-        <v>22844900</v>
+        <v>36464600</v>
       </c>
       <c r="H59" s="3">
-        <v>20918000</v>
+        <v>21624700</v>
       </c>
       <c r="I59" s="3">
-        <v>19653500</v>
+        <v>19800700</v>
       </c>
       <c r="J59" s="3">
+        <v>18603700</v>
+      </c>
+      <c r="K59" s="3">
         <v>18663100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18931600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21561700</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>62806100</v>
+        <v>65025200</v>
       </c>
       <c r="E60" s="3">
-        <v>59043400</v>
+        <v>59451400</v>
       </c>
       <c r="F60" s="3">
-        <v>49563300</v>
+        <v>55889800</v>
       </c>
       <c r="G60" s="3">
-        <v>42060600</v>
+        <v>46916000</v>
       </c>
       <c r="H60" s="3">
-        <v>40978000</v>
+        <v>39814000</v>
       </c>
       <c r="I60" s="3">
-        <v>37882400</v>
+        <v>38789200</v>
       </c>
       <c r="J60" s="3">
+        <v>35859100</v>
+      </c>
+      <c r="K60" s="3">
         <v>35194500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35506000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>40479900</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11914300</v>
+        <v>13130800</v>
       </c>
       <c r="E61" s="3">
-        <v>8112600</v>
+        <v>11277900</v>
       </c>
       <c r="F61" s="3">
-        <v>7101500</v>
+        <v>7679300</v>
       </c>
       <c r="G61" s="3">
-        <v>4279700</v>
+        <v>6722200</v>
       </c>
       <c r="H61" s="3">
-        <v>3830800</v>
+        <v>4051100</v>
       </c>
       <c r="I61" s="3">
-        <v>4202100</v>
+        <v>3626200</v>
       </c>
       <c r="J61" s="3">
+        <v>3977600</v>
+      </c>
+      <c r="K61" s="3">
         <v>4593100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4091000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6074100</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>174053000</v>
+        <v>89965800</v>
       </c>
       <c r="E62" s="3">
-        <v>89776300</v>
+        <v>164756000</v>
       </c>
       <c r="F62" s="3">
-        <v>91540600</v>
+        <v>84981100</v>
       </c>
       <c r="G62" s="3">
-        <v>76611100</v>
+        <v>86651200</v>
       </c>
       <c r="H62" s="3">
-        <v>66644500</v>
+        <v>72519100</v>
       </c>
       <c r="I62" s="3">
-        <v>61773300</v>
+        <v>63084900</v>
       </c>
       <c r="J62" s="3">
+        <v>58473800</v>
+      </c>
+      <c r="K62" s="3">
         <v>58030600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>59933000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>63488300</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2365,9 +2513,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2398,9 +2549,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2431,42 +2585,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>165505000</v>
+        <v>169200000</v>
       </c>
       <c r="E66" s="3">
-        <v>157288000</v>
+        <v>156665000</v>
       </c>
       <c r="F66" s="3">
-        <v>140377000</v>
+        <v>148887000</v>
       </c>
       <c r="G66" s="3">
-        <v>127481000</v>
+        <v>132880000</v>
       </c>
       <c r="H66" s="3">
-        <v>116165000</v>
+        <v>120672000</v>
       </c>
       <c r="I66" s="3">
-        <v>108502000</v>
+        <v>109961000</v>
       </c>
       <c r="J66" s="3">
+        <v>102706000</v>
+      </c>
+      <c r="K66" s="3">
         <v>102201000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>104444000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>115302000</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2480,8 +2640,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2512,9 +2673,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2545,9 +2709,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2578,9 +2745,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2611,42 +2781,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>34323100</v>
+        <v>38295400</v>
       </c>
       <c r="E72" s="3">
-        <v>25347500</v>
+        <v>32489800</v>
       </c>
       <c r="F72" s="3">
-        <v>19643800</v>
+        <v>23993700</v>
       </c>
       <c r="G72" s="3">
-        <v>18662100</v>
+        <v>18594500</v>
       </c>
       <c r="H72" s="3">
-        <v>15640700</v>
+        <v>17665300</v>
       </c>
       <c r="I72" s="3">
-        <v>9708200</v>
+        <v>14805300</v>
       </c>
       <c r="J72" s="3">
+        <v>9189700</v>
+      </c>
+      <c r="K72" s="3">
         <v>6634600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6882000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6941400</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2677,9 +2853,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2710,9 +2889,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2743,42 +2925,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>44474100</v>
+        <v>48406200</v>
       </c>
       <c r="E76" s="3">
-        <v>48153700</v>
+        <v>42098700</v>
       </c>
       <c r="F76" s="3">
-        <v>45025500</v>
+        <v>45581700</v>
       </c>
       <c r="G76" s="3">
-        <v>27804600</v>
+        <v>42620600</v>
       </c>
       <c r="H76" s="3">
-        <v>25250600</v>
+        <v>26319500</v>
       </c>
       <c r="I76" s="3">
-        <v>20000000</v>
+        <v>23901900</v>
       </c>
       <c r="J76" s="3">
+        <v>18931800</v>
+      </c>
+      <c r="K76" s="3">
         <v>16831400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18105500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19764700</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2809,80 +2997,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6316200</v>
+        <v>6192300</v>
       </c>
       <c r="E81" s="3">
-        <v>5945900</v>
+        <v>6413700</v>
       </c>
       <c r="F81" s="3">
-        <v>6807500</v>
+        <v>5628300</v>
       </c>
       <c r="G81" s="3">
-        <v>3924000</v>
+        <v>6443900</v>
       </c>
       <c r="H81" s="3">
-        <v>6175700</v>
+        <v>3714400</v>
       </c>
       <c r="I81" s="3">
-        <v>3308000</v>
+        <v>5845800</v>
       </c>
       <c r="J81" s="3">
+        <v>3131300</v>
+      </c>
+      <c r="K81" s="3">
         <v>494000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1086300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1074600</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2896,41 +3093,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6770900</v>
+        <v>7305000</v>
       </c>
       <c r="E83" s="3">
-        <v>5629500</v>
+        <v>6409300</v>
       </c>
       <c r="F83" s="3">
-        <v>4632900</v>
+        <v>5328800</v>
       </c>
       <c r="G83" s="3">
-        <v>2808200</v>
+        <v>4385400</v>
       </c>
       <c r="H83" s="3">
-        <v>2520900</v>
+        <v>2658200</v>
       </c>
       <c r="I83" s="3">
-        <v>2436100</v>
+        <v>2386300</v>
       </c>
       <c r="J83" s="3">
+        <v>2306000</v>
+      </c>
+      <c r="K83" s="3">
         <v>2204300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2918600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3024900</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2961,9 +3162,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2994,9 +3198,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3027,9 +3234,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3060,9 +3270,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3093,42 +3306,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2121000</v>
+        <v>8761100</v>
       </c>
       <c r="E89" s="3">
-        <v>8314800</v>
+        <v>2007700</v>
       </c>
       <c r="F89" s="3">
-        <v>7685100</v>
+        <v>7870600</v>
       </c>
       <c r="G89" s="3">
-        <v>9077500</v>
+        <v>7274600</v>
       </c>
       <c r="H89" s="3">
-        <v>8458700</v>
+        <v>8592600</v>
       </c>
       <c r="I89" s="3">
-        <v>8407200</v>
+        <v>8006900</v>
       </c>
       <c r="J89" s="3">
+        <v>7958200</v>
+      </c>
+      <c r="K89" s="3">
         <v>5454400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5505800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6437100</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3142,41 +3361,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4135900</v>
+        <v>-3980800</v>
       </c>
       <c r="E91" s="3">
-        <v>-2973000</v>
+        <v>-3915000</v>
       </c>
       <c r="F91" s="3">
-        <v>-6673700</v>
+        <v>-2814200</v>
       </c>
       <c r="G91" s="3">
-        <v>-2964000</v>
+        <v>-6317300</v>
       </c>
       <c r="H91" s="3">
-        <v>-2107200</v>
+        <v>-2805700</v>
       </c>
       <c r="I91" s="3">
-        <v>-1772500</v>
+        <v>-1994700</v>
       </c>
       <c r="J91" s="3">
+        <v>-1677900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2247900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2759300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1841800</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3207,9 +3430,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3240,42 +3466,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-7095000</v>
+        <v>-5224500</v>
       </c>
       <c r="E94" s="3">
-        <v>-4912000</v>
+        <v>-6716000</v>
       </c>
       <c r="F94" s="3">
-        <v>-3800800</v>
+        <v>-4649600</v>
       </c>
       <c r="G94" s="3">
-        <v>-9114400</v>
+        <v>-3597700</v>
       </c>
       <c r="H94" s="3">
-        <v>-8812200</v>
+        <v>-8627500</v>
       </c>
       <c r="I94" s="3">
-        <v>-5547500</v>
+        <v>-8341500</v>
       </c>
       <c r="J94" s="3">
+        <v>-5251200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-8451800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7573500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5456100</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3289,41 +3521,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-583500</v>
+        <v>-629200</v>
       </c>
       <c r="E96" s="3">
-        <v>-501100</v>
+        <v>-552300</v>
       </c>
       <c r="F96" s="3">
-        <v>-413100</v>
+        <v>-474300</v>
       </c>
       <c r="G96" s="3">
-        <v>-334100</v>
+        <v>-391000</v>
       </c>
       <c r="H96" s="3">
-        <v>-256600</v>
+        <v>-316300</v>
       </c>
       <c r="I96" s="3">
-        <v>-192000</v>
+        <v>-242900</v>
       </c>
       <c r="J96" s="3">
+        <v>-181800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-170500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-93700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-112300</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3354,9 +3590,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3387,9 +3626,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3420,106 +3662,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>568200</v>
+        <v>-1344300</v>
       </c>
       <c r="E100" s="3">
-        <v>-2268500</v>
+        <v>537800</v>
       </c>
       <c r="F100" s="3">
-        <v>-2281700</v>
+        <v>-2147400</v>
       </c>
       <c r="G100" s="3">
-        <v>442500</v>
+        <v>-2159800</v>
       </c>
       <c r="H100" s="3">
-        <v>-828200</v>
+        <v>418900</v>
       </c>
       <c r="I100" s="3">
-        <v>1661100</v>
+        <v>-784000</v>
       </c>
       <c r="J100" s="3">
+        <v>1572400</v>
+      </c>
+      <c r="K100" s="3">
         <v>3048500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2793900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2245100</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>572500</v>
+        <v>527000</v>
       </c>
       <c r="E101" s="3">
-        <v>636000</v>
+        <v>541900</v>
       </c>
       <c r="F101" s="3">
-        <v>247300</v>
+        <v>602100</v>
       </c>
       <c r="G101" s="3">
-        <v>-145900</v>
+        <v>234100</v>
       </c>
       <c r="H101" s="3">
-        <v>353600</v>
+        <v>-138100</v>
       </c>
       <c r="I101" s="3">
-        <v>-357500</v>
+        <v>334700</v>
       </c>
       <c r="J101" s="3">
+        <v>-338400</v>
+      </c>
+      <c r="K101" s="3">
         <v>-209400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-474900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>436200</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3833300</v>
+        <v>2719200</v>
       </c>
       <c r="E102" s="3">
-        <v>1770300</v>
+        <v>-3628500</v>
       </c>
       <c r="F102" s="3">
-        <v>1849900</v>
+        <v>1675700</v>
       </c>
       <c r="G102" s="3">
-        <v>259800</v>
+        <v>1751000</v>
       </c>
       <c r="H102" s="3">
-        <v>-828100</v>
+        <v>245900</v>
       </c>
       <c r="I102" s="3">
-        <v>4163300</v>
+        <v>-783900</v>
       </c>
       <c r="J102" s="3">
+        <v>3941000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-158200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>251400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-827900</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
   <si>
     <t>SONY</t>
   </si>
@@ -717,25 +717,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>83072500</v>
+        <v>92447500</v>
       </c>
       <c r="E8" s="3">
-        <v>70016500</v>
+        <v>77918000</v>
       </c>
       <c r="F8" s="3">
-        <v>63299300</v>
+        <v>70442700</v>
       </c>
       <c r="G8" s="3">
-        <v>57411500</v>
+        <v>63890500</v>
       </c>
       <c r="H8" s="3">
-        <v>52698100</v>
+        <v>58645200</v>
       </c>
       <c r="I8" s="3">
-        <v>55287100</v>
+        <v>61526400</v>
       </c>
       <c r="J8" s="3">
-        <v>54510600</v>
+        <v>60662300</v>
       </c>
       <c r="K8" s="3">
         <v>51245900</v>
@@ -753,25 +753,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>52691000</v>
+        <v>58637300</v>
       </c>
       <c r="E9" s="3">
-        <v>54203700</v>
+        <v>60320700</v>
       </c>
       <c r="F9" s="3">
-        <v>46062600</v>
+        <v>51260900</v>
       </c>
       <c r="G9" s="3">
-        <v>70913500</v>
+        <v>78916300</v>
       </c>
       <c r="H9" s="3">
-        <v>34616300</v>
+        <v>38522900</v>
       </c>
       <c r="I9" s="3">
-        <v>36889100</v>
+        <v>41052200</v>
       </c>
       <c r="J9" s="3">
-        <v>36824700</v>
+        <v>40980500</v>
       </c>
       <c r="K9" s="3">
         <v>35153800</v>
@@ -789,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>30381500</v>
+        <v>33810100</v>
       </c>
       <c r="E10" s="3">
-        <v>15812800</v>
+        <v>17597300</v>
       </c>
       <c r="F10" s="3">
-        <v>17236700</v>
+        <v>19181900</v>
       </c>
       <c r="G10" s="3">
-        <v>-13502100</v>
+        <v>-15025800</v>
       </c>
       <c r="H10" s="3">
-        <v>18081700</v>
+        <v>20122300</v>
       </c>
       <c r="I10" s="3">
-        <v>18398000</v>
+        <v>20474200</v>
       </c>
       <c r="J10" s="3">
-        <v>17685900</v>
+        <v>19681800</v>
       </c>
       <c r="K10" s="3">
         <v>16092100</v>
@@ -850,16 +850,16 @@
         <v>8</v>
       </c>
       <c r="G12" s="3">
-        <v>3350600</v>
+        <v>3728700</v>
       </c>
       <c r="H12" s="3">
-        <v>3185500</v>
+        <v>3545000</v>
       </c>
       <c r="I12" s="3">
-        <v>3070100</v>
+        <v>3416500</v>
       </c>
       <c r="J12" s="3">
-        <v>2925300</v>
+        <v>3255500</v>
       </c>
       <c r="K12" s="3">
         <v>3015900</v>
@@ -922,16 +922,16 @@
         <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>152100</v>
+        <v>169200</v>
       </c>
       <c r="H14" s="3">
-        <v>190000</v>
+        <v>211400</v>
       </c>
       <c r="I14" s="3">
-        <v>299400</v>
+        <v>333200</v>
       </c>
       <c r="J14" s="3">
-        <v>246300</v>
+        <v>274100</v>
       </c>
       <c r="K14" s="3">
         <v>755300</v>
@@ -998,25 +998,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>75360200</v>
+        <v>83864800</v>
       </c>
       <c r="E17" s="3">
-        <v>61707300</v>
+        <v>68671100</v>
       </c>
       <c r="F17" s="3">
-        <v>55628300</v>
+        <v>61906100</v>
       </c>
       <c r="G17" s="3">
-        <v>51316900</v>
+        <v>57108200</v>
       </c>
       <c r="H17" s="3">
-        <v>47304000</v>
+        <v>52642400</v>
       </c>
       <c r="I17" s="3">
-        <v>49581900</v>
+        <v>55177300</v>
       </c>
       <c r="J17" s="3">
-        <v>49822200</v>
+        <v>55444800</v>
       </c>
       <c r="K17" s="3">
         <v>49300100</v>
@@ -1034,25 +1034,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7712300</v>
+        <v>8582700</v>
       </c>
       <c r="E18" s="3">
-        <v>8309200</v>
+        <v>9247000</v>
       </c>
       <c r="F18" s="3">
-        <v>7670900</v>
+        <v>8536600</v>
       </c>
       <c r="G18" s="3">
-        <v>6094500</v>
+        <v>6782300</v>
       </c>
       <c r="H18" s="3">
-        <v>5394000</v>
+        <v>6002800</v>
       </c>
       <c r="I18" s="3">
-        <v>5705200</v>
+        <v>6349100</v>
       </c>
       <c r="J18" s="3">
-        <v>4688400</v>
+        <v>5217500</v>
       </c>
       <c r="K18" s="3">
         <v>1945900</v>
@@ -1086,25 +1086,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>381700</v>
+        <v>715900</v>
       </c>
       <c r="E20" s="3">
-        <v>-9500</v>
+        <v>-10600</v>
       </c>
       <c r="F20" s="3">
-        <v>-448100</v>
+        <v>-498700</v>
       </c>
       <c r="G20" s="3">
-        <v>440900</v>
+        <v>490600</v>
       </c>
       <c r="H20" s="3">
-        <v>-222800</v>
+        <v>-247900</v>
       </c>
       <c r="I20" s="3">
-        <v>828600</v>
+        <v>922100</v>
       </c>
       <c r="J20" s="3">
-        <v>-141900</v>
+        <v>-157900</v>
       </c>
       <c r="K20" s="3">
         <v>-151900</v>
@@ -1122,25 +1122,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>15387600</v>
+        <v>17370700</v>
       </c>
       <c r="E21" s="3">
-        <v>14698900</v>
+        <v>16318700</v>
       </c>
       <c r="F21" s="3">
-        <v>12543300</v>
+        <v>13926300</v>
       </c>
       <c r="G21" s="3">
-        <v>10914000</v>
+        <v>12118900</v>
       </c>
       <c r="H21" s="3">
-        <v>7825300</v>
+        <v>8692200</v>
       </c>
       <c r="I21" s="3">
-        <v>8916400</v>
+        <v>9908100</v>
       </c>
       <c r="J21" s="3">
-        <v>6848900</v>
+        <v>7607700</v>
       </c>
       <c r="K21" s="3">
         <v>4008100</v>
@@ -1157,26 +1157,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>291100</v>
       </c>
       <c r="E22" s="3">
-        <v>168400</v>
+        <v>187400</v>
       </c>
       <c r="F22" s="3">
-        <v>93100</v>
+        <v>103700</v>
       </c>
       <c r="G22" s="3">
-        <v>168400</v>
+        <v>187400</v>
       </c>
       <c r="H22" s="3">
-        <v>70800</v>
+        <v>78700</v>
       </c>
       <c r="I22" s="3">
-        <v>79500</v>
+        <v>88500</v>
       </c>
       <c r="J22" s="3">
-        <v>86600</v>
+        <v>96300</v>
       </c>
       <c r="K22" s="3">
         <v>98000</v>
@@ -1194,25 +1194,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>8094100</v>
+        <v>9007500</v>
       </c>
       <c r="E23" s="3">
-        <v>8131300</v>
+        <v>9048900</v>
       </c>
       <c r="F23" s="3">
-        <v>7129700</v>
+        <v>7934300</v>
       </c>
       <c r="G23" s="3">
-        <v>6367000</v>
+        <v>7085600</v>
       </c>
       <c r="H23" s="3">
-        <v>5100500</v>
+        <v>5676100</v>
       </c>
       <c r="I23" s="3">
-        <v>6454300</v>
+        <v>7182700</v>
       </c>
       <c r="J23" s="3">
-        <v>4459900</v>
+        <v>4963200</v>
       </c>
       <c r="K23" s="3">
         <v>1695900</v>
@@ -1230,25 +1230,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1838500</v>
+        <v>2046000</v>
       </c>
       <c r="E24" s="3">
-        <v>1676200</v>
+        <v>1865300</v>
       </c>
       <c r="F24" s="3">
-        <v>1461600</v>
+        <v>1626600</v>
       </c>
       <c r="G24" s="3">
-        <v>-293000</v>
+        <v>-326100</v>
       </c>
       <c r="H24" s="3">
-        <v>1130500</v>
+        <v>1258000</v>
       </c>
       <c r="I24" s="3">
-        <v>287700</v>
+        <v>320200</v>
       </c>
       <c r="J24" s="3">
-        <v>968300</v>
+        <v>1077600</v>
       </c>
       <c r="K24" s="3">
         <v>836200</v>
@@ -1302,25 +1302,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>6255600</v>
+        <v>6961500</v>
       </c>
       <c r="E26" s="3">
-        <v>6455100</v>
+        <v>7183600</v>
       </c>
       <c r="F26" s="3">
-        <v>5668000</v>
+        <v>6307700</v>
       </c>
       <c r="G26" s="3">
-        <v>6660100</v>
+        <v>7411700</v>
       </c>
       <c r="H26" s="3">
-        <v>3970000</v>
+        <v>4418000</v>
       </c>
       <c r="I26" s="3">
-        <v>6166600</v>
+        <v>6862500</v>
       </c>
       <c r="J26" s="3">
-        <v>3491600</v>
+        <v>3885700</v>
       </c>
       <c r="K26" s="3">
         <v>859800</v>
@@ -1338,25 +1338,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6192300</v>
+        <v>6891100</v>
       </c>
       <c r="E27" s="3">
-        <v>6413700</v>
+        <v>7137500</v>
       </c>
       <c r="F27" s="3">
-        <v>5628300</v>
+        <v>6263500</v>
       </c>
       <c r="G27" s="3">
-        <v>6443900</v>
+        <v>7171100</v>
       </c>
       <c r="H27" s="3">
-        <v>3714400</v>
+        <v>4133600</v>
       </c>
       <c r="I27" s="3">
-        <v>5845800</v>
+        <v>6505500</v>
       </c>
       <c r="J27" s="3">
-        <v>3131300</v>
+        <v>3484600</v>
       </c>
       <c r="K27" s="3">
         <v>494000</v>
@@ -1518,25 +1518,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-381700</v>
+        <v>-715900</v>
       </c>
       <c r="E32" s="3">
-        <v>9500</v>
+        <v>10600</v>
       </c>
       <c r="F32" s="3">
-        <v>448100</v>
+        <v>498700</v>
       </c>
       <c r="G32" s="3">
-        <v>-440900</v>
+        <v>-490600</v>
       </c>
       <c r="H32" s="3">
-        <v>222800</v>
+        <v>247900</v>
       </c>
       <c r="I32" s="3">
-        <v>-828600</v>
+        <v>-922100</v>
       </c>
       <c r="J32" s="3">
-        <v>141900</v>
+        <v>157900</v>
       </c>
       <c r="K32" s="3">
         <v>151900</v>
@@ -1554,25 +1554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6192300</v>
+        <v>6891100</v>
       </c>
       <c r="E33" s="3">
-        <v>6413700</v>
+        <v>7137500</v>
       </c>
       <c r="F33" s="3">
-        <v>5628300</v>
+        <v>6263500</v>
       </c>
       <c r="G33" s="3">
-        <v>6443900</v>
+        <v>7171100</v>
       </c>
       <c r="H33" s="3">
-        <v>3714400</v>
+        <v>4133600</v>
       </c>
       <c r="I33" s="3">
-        <v>5845800</v>
+        <v>6505500</v>
       </c>
       <c r="J33" s="3">
-        <v>3131300</v>
+        <v>3484600</v>
       </c>
       <c r="K33" s="3">
         <v>494000</v>
@@ -1626,25 +1626,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6192300</v>
+        <v>6891100</v>
       </c>
       <c r="E35" s="3">
-        <v>6413700</v>
+        <v>7137500</v>
       </c>
       <c r="F35" s="3">
-        <v>5628300</v>
+        <v>6263500</v>
       </c>
       <c r="G35" s="3">
-        <v>6443900</v>
+        <v>7171100</v>
       </c>
       <c r="H35" s="3">
-        <v>3714400</v>
+        <v>4133600</v>
       </c>
       <c r="I35" s="3">
-        <v>5845800</v>
+        <v>6505500</v>
       </c>
       <c r="J35" s="3">
-        <v>3131300</v>
+        <v>3484600</v>
       </c>
       <c r="K35" s="3">
         <v>494000</v>
@@ -1735,25 +1735,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>12167400</v>
+        <v>13540500</v>
       </c>
       <c r="E41" s="3">
-        <v>9448100</v>
+        <v>10514400</v>
       </c>
       <c r="F41" s="3">
-        <v>13076700</v>
+        <v>14552400</v>
       </c>
       <c r="G41" s="3">
-        <v>22801900</v>
+        <v>25375100</v>
       </c>
       <c r="H41" s="3">
-        <v>9648800</v>
+        <v>10737700</v>
       </c>
       <c r="I41" s="3">
-        <v>9379100</v>
+        <v>10437500</v>
       </c>
       <c r="J41" s="3">
-        <v>10120800</v>
+        <v>11262900</v>
       </c>
       <c r="K41" s="3">
         <v>6471400</v>
@@ -1771,25 +1771,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3340000</v>
+        <v>3717000</v>
       </c>
       <c r="E42" s="3">
-        <v>2802800</v>
+        <v>3119100</v>
       </c>
       <c r="F42" s="3">
-        <v>3253600</v>
+        <v>3620800</v>
       </c>
       <c r="G42" s="3">
-        <v>21896800</v>
+        <v>24367900</v>
       </c>
       <c r="H42" s="3">
-        <v>11788800</v>
+        <v>13119200</v>
       </c>
       <c r="I42" s="3">
-        <v>8450600</v>
+        <v>9404200</v>
       </c>
       <c r="J42" s="3">
-        <v>7506700</v>
+        <v>8353900</v>
       </c>
       <c r="K42" s="3">
         <v>7086700</v>
@@ -1807,25 +1807,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13769300</v>
+        <v>15323200</v>
       </c>
       <c r="E43" s="3">
-        <v>11298600</v>
+        <v>12573700</v>
       </c>
       <c r="F43" s="3">
-        <v>10390000</v>
+        <v>11562500</v>
       </c>
       <c r="G43" s="3">
-        <v>17346500</v>
+        <v>19304100</v>
       </c>
       <c r="H43" s="3">
-        <v>7598700</v>
+        <v>8456300</v>
       </c>
       <c r="I43" s="3">
-        <v>8226500</v>
+        <v>9154900</v>
       </c>
       <c r="J43" s="3">
-        <v>7678200</v>
+        <v>8544700</v>
       </c>
       <c r="K43" s="3">
         <v>7936000</v>
@@ -1843,25 +1843,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9688900</v>
+        <v>10782400</v>
       </c>
       <c r="E44" s="3">
-        <v>18732200</v>
+        <v>20846200</v>
       </c>
       <c r="F44" s="3">
-        <v>5576200</v>
+        <v>6205400</v>
       </c>
       <c r="G44" s="3">
-        <v>8123900</v>
+        <v>9040700</v>
       </c>
       <c r="H44" s="3">
-        <v>3764000</v>
+        <v>4188800</v>
       </c>
       <c r="I44" s="3">
-        <v>4167900</v>
+        <v>4638300</v>
       </c>
       <c r="J44" s="3">
-        <v>4420900</v>
+        <v>4919900</v>
       </c>
       <c r="K44" s="3">
         <v>4319200</v>
@@ -1879,25 +1879,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4270400</v>
+        <v>4752300</v>
       </c>
       <c r="E45" s="3">
-        <v>3594100</v>
+        <v>3999700</v>
       </c>
       <c r="F45" s="3">
-        <v>3018200</v>
+        <v>3358800</v>
       </c>
       <c r="G45" s="3">
-        <v>5963700</v>
+        <v>6636700</v>
       </c>
       <c r="H45" s="3">
-        <v>3789900</v>
+        <v>4217500</v>
       </c>
       <c r="I45" s="3">
-        <v>3249300</v>
+        <v>3616000</v>
       </c>
       <c r="J45" s="3">
-        <v>3296800</v>
+        <v>3668900</v>
       </c>
       <c r="K45" s="3">
         <v>3544300</v>
@@ -1915,25 +1915,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>43236000</v>
+        <v>48115300</v>
       </c>
       <c r="E46" s="3">
-        <v>36509800</v>
+        <v>40630000</v>
       </c>
       <c r="F46" s="3">
-        <v>35314600</v>
+        <v>39300000</v>
       </c>
       <c r="G46" s="3">
-        <v>30081800</v>
+        <v>33476600</v>
       </c>
       <c r="H46" s="3">
-        <v>36590200</v>
+        <v>40719500</v>
       </c>
       <c r="I46" s="3">
-        <v>33473400</v>
+        <v>37250900</v>
       </c>
       <c r="J46" s="3">
-        <v>33023500</v>
+        <v>36750300</v>
       </c>
       <c r="K46" s="3">
         <v>29357600</v>
@@ -1951,25 +1951,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>129264000</v>
+        <v>143852000</v>
       </c>
       <c r="E47" s="3">
-        <v>123742000</v>
+        <v>137707000</v>
       </c>
       <c r="F47" s="3">
-        <v>123835000</v>
+        <v>137810000</v>
       </c>
       <c r="G47" s="3">
-        <v>207231000</v>
+        <v>230618000</v>
       </c>
       <c r="H47" s="3">
-        <v>81243800</v>
+        <v>90412300</v>
       </c>
       <c r="I47" s="3">
-        <v>74803300</v>
+        <v>83245000</v>
       </c>
       <c r="J47" s="3">
-        <v>68623700</v>
+        <v>76368000</v>
       </c>
       <c r="K47" s="3">
         <v>68153500</v>
@@ -1987,25 +1987,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12926100</v>
+        <v>14384800</v>
       </c>
       <c r="E48" s="3">
-        <v>23260500</v>
+        <v>25885600</v>
       </c>
       <c r="F48" s="3">
-        <v>9740000</v>
+        <v>10839200</v>
       </c>
       <c r="G48" s="3">
-        <v>6948800</v>
+        <v>7733000</v>
       </c>
       <c r="H48" s="3">
-        <v>8302000</v>
+        <v>9238900</v>
       </c>
       <c r="I48" s="3">
-        <v>4957600</v>
+        <v>5517100</v>
       </c>
       <c r="J48" s="3">
-        <v>4717800</v>
+        <v>5250200</v>
       </c>
       <c r="K48" s="3">
         <v>5110300</v>
@@ -2023,25 +2023,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>25716600</v>
+        <v>28618800</v>
       </c>
       <c r="E49" s="3">
-        <v>43394700</v>
+        <v>48291900</v>
       </c>
       <c r="F49" s="3">
-        <v>17513400</v>
+        <v>19489800</v>
       </c>
       <c r="G49" s="3">
-        <v>33447800</v>
+        <v>37222500</v>
       </c>
       <c r="H49" s="3">
-        <v>10783500</v>
+        <v>12000400</v>
       </c>
       <c r="I49" s="3">
-        <v>10760000</v>
+        <v>11974300</v>
       </c>
       <c r="J49" s="3">
-        <v>6747900</v>
+        <v>7509400</v>
       </c>
       <c r="K49" s="3">
         <v>7459300</v>
@@ -2131,25 +2131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6462700</v>
+        <v>7192000</v>
       </c>
       <c r="E52" s="3">
-        <v>9846500</v>
+        <v>10957700</v>
       </c>
       <c r="F52" s="3">
-        <v>8065400</v>
+        <v>8975600</v>
       </c>
       <c r="G52" s="3">
-        <v>13243900</v>
+        <v>14738500</v>
       </c>
       <c r="H52" s="3">
-        <v>10071600</v>
+        <v>11208200</v>
       </c>
       <c r="I52" s="3">
-        <v>9868300</v>
+        <v>10981900</v>
       </c>
       <c r="J52" s="3">
-        <v>8525300</v>
+        <v>9487400</v>
       </c>
       <c r="K52" s="3">
         <v>8951500</v>
@@ -2203,25 +2203,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>217606000</v>
+        <v>242163000</v>
       </c>
       <c r="E54" s="3">
-        <v>198763000</v>
+        <v>221194000</v>
       </c>
       <c r="F54" s="3">
-        <v>194469000</v>
+        <v>216415000</v>
       </c>
       <c r="G54" s="3">
-        <v>175500000</v>
+        <v>195306000</v>
       </c>
       <c r="H54" s="3">
-        <v>146991000</v>
+        <v>163579000</v>
       </c>
       <c r="I54" s="3">
-        <v>133863000</v>
+        <v>148969000</v>
       </c>
       <c r="J54" s="3">
-        <v>121638000</v>
+        <v>135365000</v>
       </c>
       <c r="K54" s="3">
         <v>119032000</v>
@@ -2271,25 +2271,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>13174100</v>
+        <v>14660800</v>
       </c>
       <c r="E57" s="3">
-        <v>11905700</v>
+        <v>13249300</v>
       </c>
       <c r="F57" s="3">
-        <v>11759900</v>
+        <v>13087000</v>
       </c>
       <c r="G57" s="3">
-        <v>25219900</v>
+        <v>28066100</v>
       </c>
       <c r="H57" s="3">
-        <v>12830200</v>
+        <v>14278100</v>
       </c>
       <c r="I57" s="3">
-        <v>13941400</v>
+        <v>15514700</v>
       </c>
       <c r="J57" s="3">
-        <v>12651400</v>
+        <v>14079200</v>
       </c>
       <c r="K57" s="3">
         <v>13039600</v>
@@ -2307,25 +2307,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12953400</v>
+        <v>14415200</v>
       </c>
       <c r="E58" s="3">
-        <v>13416300</v>
+        <v>14930400</v>
       </c>
       <c r="F58" s="3">
-        <v>13704000</v>
+        <v>15250500</v>
       </c>
       <c r="G58" s="3">
-        <v>9817900</v>
+        <v>10925800</v>
       </c>
       <c r="H58" s="3">
-        <v>5359100</v>
+        <v>5963900</v>
       </c>
       <c r="I58" s="3">
-        <v>5047100</v>
+        <v>5616700</v>
       </c>
       <c r="J58" s="3">
-        <v>4603900</v>
+        <v>5123500</v>
       </c>
       <c r="K58" s="3">
         <v>3491900</v>
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>38897700</v>
+        <v>43287500</v>
       </c>
       <c r="E59" s="3">
-        <v>34129400</v>
+        <v>37981000</v>
       </c>
       <c r="F59" s="3">
-        <v>30425900</v>
+        <v>33859500</v>
       </c>
       <c r="G59" s="3">
-        <v>36464600</v>
+        <v>40579800</v>
       </c>
       <c r="H59" s="3">
-        <v>21624700</v>
+        <v>24065100</v>
       </c>
       <c r="I59" s="3">
-        <v>19800700</v>
+        <v>22035300</v>
       </c>
       <c r="J59" s="3">
-        <v>18603700</v>
+        <v>20703200</v>
       </c>
       <c r="K59" s="3">
         <v>18663100</v>
@@ -2379,25 +2379,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>65025200</v>
+        <v>72363500</v>
       </c>
       <c r="E60" s="3">
-        <v>59451400</v>
+        <v>66160700</v>
       </c>
       <c r="F60" s="3">
-        <v>55889800</v>
+        <v>62197100</v>
       </c>
       <c r="G60" s="3">
-        <v>46916000</v>
+        <v>52210600</v>
       </c>
       <c r="H60" s="3">
-        <v>39814000</v>
+        <v>44307100</v>
       </c>
       <c r="I60" s="3">
-        <v>38789200</v>
+        <v>43166700</v>
       </c>
       <c r="J60" s="3">
-        <v>35859100</v>
+        <v>39905800</v>
       </c>
       <c r="K60" s="3">
         <v>35194500</v>
@@ -2415,25 +2415,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13130800</v>
+        <v>14612600</v>
       </c>
       <c r="E61" s="3">
-        <v>11277900</v>
+        <v>12550600</v>
       </c>
       <c r="F61" s="3">
-        <v>7679300</v>
+        <v>8545900</v>
       </c>
       <c r="G61" s="3">
-        <v>6722200</v>
+        <v>7480800</v>
       </c>
       <c r="H61" s="3">
-        <v>4051100</v>
+        <v>4508300</v>
       </c>
       <c r="I61" s="3">
-        <v>3626200</v>
+        <v>4035400</v>
       </c>
       <c r="J61" s="3">
-        <v>3977600</v>
+        <v>4426500</v>
       </c>
       <c r="K61" s="3">
         <v>4593100</v>
@@ -2451,25 +2451,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>89965800</v>
+        <v>100119000</v>
       </c>
       <c r="E62" s="3">
-        <v>164756000</v>
+        <v>183349000</v>
       </c>
       <c r="F62" s="3">
-        <v>84981100</v>
+        <v>94571400</v>
       </c>
       <c r="G62" s="3">
-        <v>86651200</v>
+        <v>96430000</v>
       </c>
       <c r="H62" s="3">
-        <v>72519100</v>
+        <v>80703100</v>
       </c>
       <c r="I62" s="3">
-        <v>63084900</v>
+        <v>70204100</v>
       </c>
       <c r="J62" s="3">
-        <v>58473800</v>
+        <v>65072800</v>
       </c>
       <c r="K62" s="3">
         <v>58030600</v>
@@ -2595,25 +2595,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>169200000</v>
+        <v>188294000</v>
       </c>
       <c r="E66" s="3">
-        <v>156665000</v>
+        <v>174345000</v>
       </c>
       <c r="F66" s="3">
-        <v>148887000</v>
+        <v>165689000</v>
       </c>
       <c r="G66" s="3">
-        <v>132880000</v>
+        <v>147875000</v>
       </c>
       <c r="H66" s="3">
-        <v>120672000</v>
+        <v>134290000</v>
       </c>
       <c r="I66" s="3">
-        <v>109961000</v>
+        <v>122370000</v>
       </c>
       <c r="J66" s="3">
-        <v>102706000</v>
+        <v>114297000</v>
       </c>
       <c r="K66" s="3">
         <v>102201000</v>
@@ -2791,25 +2791,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>38295400</v>
+        <v>42617100</v>
       </c>
       <c r="E72" s="3">
-        <v>32489800</v>
+        <v>36156300</v>
       </c>
       <c r="F72" s="3">
-        <v>23993700</v>
+        <v>26701400</v>
       </c>
       <c r="G72" s="3">
-        <v>18594500</v>
+        <v>20693000</v>
       </c>
       <c r="H72" s="3">
-        <v>17665300</v>
+        <v>19658900</v>
       </c>
       <c r="I72" s="3">
-        <v>14805300</v>
+        <v>16476200</v>
       </c>
       <c r="J72" s="3">
-        <v>9189700</v>
+        <v>10226700</v>
       </c>
       <c r="K72" s="3">
         <v>6634600</v>
@@ -2935,25 +2935,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>48406200</v>
+        <v>53869000</v>
       </c>
       <c r="E76" s="3">
-        <v>42098700</v>
+        <v>46849600</v>
       </c>
       <c r="F76" s="3">
-        <v>45581700</v>
+        <v>50725700</v>
       </c>
       <c r="G76" s="3">
-        <v>42620600</v>
+        <v>47430400</v>
       </c>
       <c r="H76" s="3">
-        <v>26319500</v>
+        <v>29289700</v>
       </c>
       <c r="I76" s="3">
-        <v>23901900</v>
+        <v>26599300</v>
       </c>
       <c r="J76" s="3">
-        <v>18931800</v>
+        <v>21068300</v>
       </c>
       <c r="K76" s="3">
         <v>16831400</v>
@@ -3048,25 +3048,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6192300</v>
+        <v>6891100</v>
       </c>
       <c r="E81" s="3">
-        <v>6413700</v>
+        <v>7137500</v>
       </c>
       <c r="F81" s="3">
-        <v>5628300</v>
+        <v>6263500</v>
       </c>
       <c r="G81" s="3">
-        <v>6443900</v>
+        <v>7171100</v>
       </c>
       <c r="H81" s="3">
-        <v>3714400</v>
+        <v>4133600</v>
       </c>
       <c r="I81" s="3">
-        <v>5845800</v>
+        <v>6505500</v>
       </c>
       <c r="J81" s="3">
-        <v>3131300</v>
+        <v>3484600</v>
       </c>
       <c r="K81" s="3">
         <v>494000</v>
@@ -3100,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7305000</v>
+        <v>8129400</v>
       </c>
       <c r="E83" s="3">
-        <v>6409300</v>
+        <v>7132600</v>
       </c>
       <c r="F83" s="3">
-        <v>5328800</v>
+        <v>5930200</v>
       </c>
       <c r="G83" s="3">
-        <v>4385400</v>
+        <v>4880300</v>
       </c>
       <c r="H83" s="3">
-        <v>2658200</v>
+        <v>2958200</v>
       </c>
       <c r="I83" s="3">
-        <v>2386300</v>
+        <v>2655600</v>
       </c>
       <c r="J83" s="3">
-        <v>2306000</v>
+        <v>2566300</v>
       </c>
       <c r="K83" s="3">
         <v>2204300</v>
@@ -3316,25 +3316,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>8761100</v>
+        <v>9749800</v>
       </c>
       <c r="E89" s="3">
-        <v>2007700</v>
+        <v>2234300</v>
       </c>
       <c r="F89" s="3">
-        <v>7870600</v>
+        <v>8758900</v>
       </c>
       <c r="G89" s="3">
-        <v>7274600</v>
+        <v>8095500</v>
       </c>
       <c r="H89" s="3">
-        <v>8592600</v>
+        <v>9562300</v>
       </c>
       <c r="I89" s="3">
-        <v>8006900</v>
+        <v>8910500</v>
       </c>
       <c r="J89" s="3">
-        <v>7958200</v>
+        <v>8856300</v>
       </c>
       <c r="K89" s="3">
         <v>5454400</v>
@@ -3368,25 +3368,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-3980800</v>
+        <v>-4430000</v>
       </c>
       <c r="E91" s="3">
-        <v>-3915000</v>
+        <v>-4356800</v>
       </c>
       <c r="F91" s="3">
-        <v>-2814200</v>
+        <v>-3131800</v>
       </c>
       <c r="G91" s="3">
-        <v>-6317300</v>
+        <v>-7030200</v>
       </c>
       <c r="H91" s="3">
-        <v>-2805700</v>
+        <v>-3122300</v>
       </c>
       <c r="I91" s="3">
-        <v>-1994700</v>
+        <v>-2219800</v>
       </c>
       <c r="J91" s="3">
-        <v>-1677900</v>
+        <v>-1867200</v>
       </c>
       <c r="K91" s="3">
         <v>-2247900</v>
@@ -3476,25 +3476,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5224500</v>
+        <v>-5814100</v>
       </c>
       <c r="E94" s="3">
-        <v>-6716000</v>
+        <v>-7473900</v>
       </c>
       <c r="F94" s="3">
-        <v>-4649600</v>
+        <v>-5174300</v>
       </c>
       <c r="G94" s="3">
-        <v>-3597700</v>
+        <v>-4003800</v>
       </c>
       <c r="H94" s="3">
-        <v>-8627500</v>
+        <v>-9601200</v>
       </c>
       <c r="I94" s="3">
-        <v>-8341500</v>
+        <v>-9282900</v>
       </c>
       <c r="J94" s="3">
-        <v>-5251200</v>
+        <v>-5843800</v>
       </c>
       <c r="K94" s="3">
         <v>-8451800</v>
@@ -3528,25 +3528,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-629200</v>
+        <v>-700200</v>
       </c>
       <c r="E96" s="3">
-        <v>-552300</v>
+        <v>-614600</v>
       </c>
       <c r="F96" s="3">
-        <v>-474300</v>
+        <v>-527800</v>
       </c>
       <c r="G96" s="3">
-        <v>-391000</v>
+        <v>-435100</v>
       </c>
       <c r="H96" s="3">
-        <v>-316300</v>
+        <v>-352000</v>
       </c>
       <c r="I96" s="3">
-        <v>-242900</v>
+        <v>-270300</v>
       </c>
       <c r="J96" s="3">
-        <v>-181800</v>
+        <v>-202300</v>
       </c>
       <c r="K96" s="3">
         <v>-170500</v>
@@ -3672,25 +3672,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1344300</v>
+        <v>-1496000</v>
       </c>
       <c r="E100" s="3">
-        <v>537800</v>
+        <v>598500</v>
       </c>
       <c r="F100" s="3">
-        <v>-2147400</v>
+        <v>-2389700</v>
       </c>
       <c r="G100" s="3">
-        <v>-2159800</v>
+        <v>-2403600</v>
       </c>
       <c r="H100" s="3">
-        <v>418900</v>
+        <v>466200</v>
       </c>
       <c r="I100" s="3">
-        <v>-784000</v>
+        <v>-872500</v>
       </c>
       <c r="J100" s="3">
-        <v>1572400</v>
+        <v>1749800</v>
       </c>
       <c r="K100" s="3">
         <v>3048500</v>
@@ -3708,25 +3708,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>527000</v>
+        <v>586400</v>
       </c>
       <c r="E101" s="3">
-        <v>541900</v>
+        <v>603100</v>
       </c>
       <c r="F101" s="3">
-        <v>602100</v>
+        <v>670000</v>
       </c>
       <c r="G101" s="3">
-        <v>234100</v>
+        <v>260500</v>
       </c>
       <c r="H101" s="3">
-        <v>-138100</v>
+        <v>-153700</v>
       </c>
       <c r="I101" s="3">
-        <v>334700</v>
+        <v>372500</v>
       </c>
       <c r="J101" s="3">
-        <v>-338400</v>
+        <v>-376600</v>
       </c>
       <c r="K101" s="3">
         <v>-209400</v>
@@ -3744,25 +3744,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>2719200</v>
+        <v>3026100</v>
       </c>
       <c r="E102" s="3">
-        <v>-3628500</v>
+        <v>-4038000</v>
       </c>
       <c r="F102" s="3">
-        <v>1675700</v>
+        <v>1864800</v>
       </c>
       <c r="G102" s="3">
-        <v>1751000</v>
+        <v>1948700</v>
       </c>
       <c r="H102" s="3">
-        <v>245900</v>
+        <v>273700</v>
       </c>
       <c r="I102" s="3">
-        <v>-783900</v>
+        <v>-872300</v>
       </c>
       <c r="J102" s="3">
-        <v>3941000</v>
+        <v>4385700</v>
       </c>
       <c r="K102" s="3">
         <v>-158200</v>

--- a/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
   <si>
     <t>SONY</t>
   </si>
@@ -687,7 +687,7 @@
         <v>45016</v>
       </c>
       <c r="F7" s="2">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="G7" s="2">
         <v>44286</v>
@@ -717,25 +717,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>92447500</v>
+        <v>86084900</v>
       </c>
       <c r="E8" s="3">
-        <v>77918000</v>
+        <v>82555000</v>
       </c>
       <c r="F8" s="3">
-        <v>70442700</v>
+        <v>80788200</v>
       </c>
       <c r="G8" s="3">
-        <v>63890500</v>
+        <v>81363000</v>
       </c>
       <c r="H8" s="3">
-        <v>58645200</v>
+        <v>76763300</v>
       </c>
       <c r="I8" s="3">
-        <v>61526400</v>
+        <v>78203100</v>
       </c>
       <c r="J8" s="3">
-        <v>60662300</v>
+        <v>80360300</v>
       </c>
       <c r="K8" s="3">
         <v>51245900</v>
@@ -753,25 +753,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>58637300</v>
+        <v>53379400</v>
       </c>
       <c r="E9" s="3">
-        <v>60320700</v>
+        <v>53865200</v>
       </c>
       <c r="F9" s="3">
-        <v>51260900</v>
+        <v>47600800</v>
       </c>
       <c r="G9" s="3">
-        <v>78916300</v>
+        <v>45804000</v>
       </c>
       <c r="H9" s="3">
-        <v>38522900</v>
+        <v>44173700</v>
       </c>
       <c r="I9" s="3">
-        <v>41052200</v>
+        <v>46482700</v>
       </c>
       <c r="J9" s="3">
-        <v>40980500</v>
+        <v>48851400</v>
       </c>
       <c r="K9" s="3">
         <v>35153800</v>
@@ -789,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>33810100</v>
+        <v>22085200</v>
       </c>
       <c r="E10" s="3">
-        <v>17597300</v>
+        <v>24442900</v>
       </c>
       <c r="F10" s="3">
-        <v>19181900</v>
+        <v>21999000</v>
       </c>
       <c r="G10" s="3">
-        <v>-15025800</v>
+        <v>21981300</v>
       </c>
       <c r="H10" s="3">
-        <v>20122300</v>
+        <v>21713900</v>
       </c>
       <c r="I10" s="3">
-        <v>20474200</v>
+        <v>21675000</v>
       </c>
       <c r="J10" s="3">
-        <v>19681800</v>
+        <v>21695600</v>
       </c>
       <c r="K10" s="3">
         <v>16092100</v>
@@ -840,26 +840,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>4910700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5534300</v>
+      </c>
+      <c r="F12" s="3">
+        <v>5035200</v>
       </c>
       <c r="G12" s="3">
-        <v>3728700</v>
+        <v>4930900</v>
       </c>
       <c r="H12" s="3">
-        <v>3545000</v>
+        <v>4640200</v>
       </c>
       <c r="I12" s="3">
-        <v>3416500</v>
+        <v>4342600</v>
       </c>
       <c r="J12" s="3">
-        <v>3255500</v>
+        <v>4317300</v>
       </c>
       <c r="K12" s="3">
         <v>3015900</v>
@@ -912,26 +912,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-571000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>116900</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-1000</v>
       </c>
       <c r="G14" s="3">
-        <v>169200</v>
+        <v>-434000</v>
       </c>
       <c r="H14" s="3">
-        <v>211400</v>
+        <v>381200</v>
       </c>
       <c r="I14" s="3">
-        <v>333200</v>
+        <v>-1496200</v>
       </c>
       <c r="J14" s="3">
-        <v>274100</v>
+        <v>161900</v>
       </c>
       <c r="K14" s="3">
         <v>755300</v>
@@ -949,25 +949,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2408300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2321600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>6744700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>6149300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>3810000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>3374600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2761500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -998,25 +998,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>83864800</v>
+        <v>78261400</v>
       </c>
       <c r="E17" s="3">
-        <v>68671100</v>
+        <v>72859600</v>
       </c>
       <c r="F17" s="3">
-        <v>61906100</v>
+        <v>71730200</v>
       </c>
       <c r="G17" s="3">
-        <v>57108200</v>
+        <v>72710400</v>
       </c>
       <c r="H17" s="3">
-        <v>52642400</v>
+        <v>68845400</v>
       </c>
       <c r="I17" s="3">
-        <v>55177300</v>
+        <v>70537400</v>
       </c>
       <c r="J17" s="3">
-        <v>55444800</v>
+        <v>73392800</v>
       </c>
       <c r="K17" s="3">
         <v>49300100</v>
@@ -1034,25 +1034,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8582700</v>
+        <v>7823500</v>
       </c>
       <c r="E18" s="3">
-        <v>9247000</v>
+        <v>9695500</v>
       </c>
       <c r="F18" s="3">
-        <v>8536600</v>
+        <v>9057900</v>
       </c>
       <c r="G18" s="3">
-        <v>6782300</v>
+        <v>8652500</v>
       </c>
       <c r="H18" s="3">
-        <v>6002800</v>
+        <v>7917900</v>
       </c>
       <c r="I18" s="3">
-        <v>6349100</v>
+        <v>7665700</v>
       </c>
       <c r="J18" s="3">
-        <v>5217500</v>
+        <v>6967500</v>
       </c>
       <c r="K18" s="3">
         <v>1945900</v>
@@ -1086,25 +1086,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>715900</v>
+        <v>-8100</v>
       </c>
       <c r="E20" s="3">
-        <v>-10600</v>
+        <v>-12700</v>
       </c>
       <c r="F20" s="3">
-        <v>-498700</v>
+        <v>-79800</v>
       </c>
       <c r="G20" s="3">
-        <v>490600</v>
+        <v>17800</v>
       </c>
       <c r="H20" s="3">
-        <v>-247900</v>
+        <v>183100</v>
       </c>
       <c r="I20" s="3">
-        <v>922100</v>
+        <v>114900</v>
       </c>
       <c r="J20" s="3">
-        <v>-157900</v>
+        <v>282100</v>
       </c>
       <c r="K20" s="3">
         <v>-151900</v>
@@ -1122,25 +1122,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17370700</v>
+        <v>10239900</v>
       </c>
       <c r="E21" s="3">
-        <v>16318700</v>
+        <v>12029700</v>
       </c>
       <c r="F21" s="3">
-        <v>13926300</v>
+        <v>15882500</v>
       </c>
       <c r="G21" s="3">
-        <v>12118900</v>
+        <v>14784000</v>
       </c>
       <c r="H21" s="3">
-        <v>8692200</v>
+        <v>11544900</v>
       </c>
       <c r="I21" s="3">
-        <v>9908100</v>
+        <v>10925400</v>
       </c>
       <c r="J21" s="3">
-        <v>7607700</v>
+        <v>9446900</v>
       </c>
       <c r="K21" s="3">
         <v>4008100</v>
@@ -1158,25 +1158,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>291100</v>
+        <v>271000</v>
       </c>
       <c r="E22" s="3">
-        <v>187400</v>
+        <v>198600</v>
       </c>
       <c r="F22" s="3">
-        <v>103700</v>
+        <v>118900</v>
       </c>
       <c r="G22" s="3">
-        <v>187400</v>
+        <v>128500</v>
       </c>
       <c r="H22" s="3">
-        <v>78700</v>
+        <v>103100</v>
       </c>
       <c r="I22" s="3">
-        <v>88500</v>
+        <v>112500</v>
       </c>
       <c r="J22" s="3">
-        <v>96300</v>
+        <v>127700</v>
       </c>
       <c r="K22" s="3">
         <v>98000</v>
@@ -1194,25 +1194,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>9007500</v>
+        <v>8387600</v>
       </c>
       <c r="E23" s="3">
-        <v>9048900</v>
+        <v>9587400</v>
       </c>
       <c r="F23" s="3">
-        <v>7934300</v>
+        <v>9099500</v>
       </c>
       <c r="G23" s="3">
-        <v>7085600</v>
+        <v>9023300</v>
       </c>
       <c r="H23" s="3">
-        <v>5676100</v>
+        <v>7429700</v>
       </c>
       <c r="I23" s="3">
-        <v>7182700</v>
+        <v>9129600</v>
       </c>
       <c r="J23" s="3">
-        <v>4963200</v>
+        <v>6582100</v>
       </c>
       <c r="K23" s="3">
         <v>1695900</v>
@@ -1230,25 +1230,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2046000</v>
+        <v>1905200</v>
       </c>
       <c r="E24" s="3">
-        <v>1865300</v>
+        <v>1976300</v>
       </c>
       <c r="F24" s="3">
-        <v>1626600</v>
+        <v>1865500</v>
       </c>
       <c r="G24" s="3">
-        <v>-326100</v>
+        <v>-415300</v>
       </c>
       <c r="H24" s="3">
-        <v>1258000</v>
+        <v>1646700</v>
       </c>
       <c r="I24" s="3">
-        <v>320200</v>
+        <v>407000</v>
       </c>
       <c r="J24" s="3">
-        <v>1077600</v>
+        <v>1429000</v>
       </c>
       <c r="K24" s="3">
         <v>836200</v>
@@ -1302,25 +1302,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>6961500</v>
+        <v>6482400</v>
       </c>
       <c r="E26" s="3">
-        <v>7183600</v>
+        <v>7611100</v>
       </c>
       <c r="F26" s="3">
-        <v>6307700</v>
+        <v>7234000</v>
       </c>
       <c r="G26" s="3">
-        <v>7411700</v>
+        <v>9438600</v>
       </c>
       <c r="H26" s="3">
-        <v>4418000</v>
+        <v>5783000</v>
       </c>
       <c r="I26" s="3">
-        <v>6862500</v>
+        <v>8722600</v>
       </c>
       <c r="J26" s="3">
-        <v>3885700</v>
+        <v>5153000</v>
       </c>
       <c r="K26" s="3">
         <v>859800</v>
@@ -1338,25 +1338,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6891100</v>
+        <v>6416800</v>
       </c>
       <c r="E27" s="3">
-        <v>7137500</v>
+        <v>7562200</v>
       </c>
       <c r="F27" s="3">
-        <v>6263500</v>
+        <v>7183300</v>
       </c>
       <c r="G27" s="3">
-        <v>7171100</v>
+        <v>9309400</v>
       </c>
       <c r="H27" s="3">
-        <v>4133600</v>
+        <v>5410600</v>
       </c>
       <c r="I27" s="3">
-        <v>6505500</v>
+        <v>8268900</v>
       </c>
       <c r="J27" s="3">
-        <v>3484600</v>
+        <v>4621200</v>
       </c>
       <c r="K27" s="3">
         <v>494000</v>
@@ -1518,25 +1518,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-715900</v>
+        <v>8100</v>
       </c>
       <c r="E32" s="3">
-        <v>10600</v>
+        <v>12700</v>
       </c>
       <c r="F32" s="3">
-        <v>498700</v>
+        <v>79800</v>
       </c>
       <c r="G32" s="3">
-        <v>-490600</v>
+        <v>-17800</v>
       </c>
       <c r="H32" s="3">
-        <v>247900</v>
+        <v>-183100</v>
       </c>
       <c r="I32" s="3">
-        <v>-922100</v>
+        <v>-114900</v>
       </c>
       <c r="J32" s="3">
-        <v>157900</v>
+        <v>-282100</v>
       </c>
       <c r="K32" s="3">
         <v>151900</v>
@@ -1554,25 +1554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6891100</v>
+        <v>6416800</v>
       </c>
       <c r="E33" s="3">
-        <v>7137500</v>
+        <v>7562200</v>
       </c>
       <c r="F33" s="3">
-        <v>6263500</v>
+        <v>7183300</v>
       </c>
       <c r="G33" s="3">
-        <v>7171100</v>
+        <v>9309400</v>
       </c>
       <c r="H33" s="3">
-        <v>4133600</v>
+        <v>5410600</v>
       </c>
       <c r="I33" s="3">
-        <v>6505500</v>
+        <v>8268800</v>
       </c>
       <c r="J33" s="3">
-        <v>3484600</v>
+        <v>4621200</v>
       </c>
       <c r="K33" s="3">
         <v>494000</v>
@@ -1626,25 +1626,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6891100</v>
+        <v>6416800</v>
       </c>
       <c r="E35" s="3">
-        <v>7137500</v>
+        <v>7562200</v>
       </c>
       <c r="F35" s="3">
-        <v>6263500</v>
+        <v>7183300</v>
       </c>
       <c r="G35" s="3">
-        <v>7171100</v>
+        <v>9309400</v>
       </c>
       <c r="H35" s="3">
-        <v>4133600</v>
+        <v>5410600</v>
       </c>
       <c r="I35" s="3">
-        <v>6505500</v>
+        <v>8268800</v>
       </c>
       <c r="J35" s="3">
-        <v>3484600</v>
+        <v>4621200</v>
       </c>
       <c r="K35" s="3">
         <v>494000</v>
@@ -1673,7 +1673,7 @@
         <v>45016</v>
       </c>
       <c r="F38" s="2">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="G38" s="2">
         <v>44286</v>
@@ -1735,25 +1735,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13540500</v>
+        <v>6567000</v>
       </c>
       <c r="E41" s="3">
-        <v>10514400</v>
+        <v>5449400</v>
       </c>
       <c r="F41" s="3">
-        <v>14552400</v>
+        <v>9449600</v>
       </c>
       <c r="G41" s="3">
-        <v>25375100</v>
+        <v>11661600</v>
       </c>
       <c r="H41" s="3">
-        <v>10737700</v>
+        <v>8943300</v>
       </c>
       <c r="I41" s="3">
-        <v>10437500</v>
+        <v>8667800</v>
       </c>
       <c r="J41" s="3">
-        <v>11262900</v>
+        <v>14936500</v>
       </c>
       <c r="K41" s="3">
         <v>6471400</v>
@@ -1771,25 +1771,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3717000</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>3119100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>3620800</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>24367900</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>13119200</v>
+        <v>195700</v>
       </c>
       <c r="I42" s="3">
-        <v>9404200</v>
+        <v>400</v>
       </c>
       <c r="J42" s="3">
-        <v>8353900</v>
+        <v>11078800</v>
       </c>
       <c r="K42" s="3">
         <v>7086700</v>
@@ -1807,25 +1807,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>15323200</v>
+        <v>14268600</v>
       </c>
       <c r="E43" s="3">
-        <v>12573700</v>
+        <v>13322000</v>
       </c>
       <c r="F43" s="3">
-        <v>11562500</v>
+        <v>13204500</v>
       </c>
       <c r="G43" s="3">
-        <v>19304100</v>
+        <v>12346300</v>
       </c>
       <c r="H43" s="3">
-        <v>8456300</v>
+        <v>11068800</v>
       </c>
       <c r="I43" s="3">
-        <v>9154900</v>
+        <v>11636300</v>
       </c>
       <c r="J43" s="3">
-        <v>8544700</v>
+        <v>11331700</v>
       </c>
       <c r="K43" s="3">
         <v>7936000</v>
@@ -1843,25 +1843,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>10782400</v>
+        <v>10040300</v>
       </c>
       <c r="E44" s="3">
-        <v>20846200</v>
+        <v>11043400</v>
       </c>
       <c r="F44" s="3">
-        <v>6205400</v>
+        <v>7116800</v>
       </c>
       <c r="G44" s="3">
-        <v>9040700</v>
+        <v>5756500</v>
       </c>
       <c r="H44" s="3">
-        <v>4188800</v>
+        <v>5482900</v>
       </c>
       <c r="I44" s="3">
-        <v>4638300</v>
+        <v>5895500</v>
       </c>
       <c r="J44" s="3">
-        <v>4919900</v>
+        <v>6524500</v>
       </c>
       <c r="K44" s="3">
         <v>4319200</v>
@@ -1879,25 +1879,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4752300</v>
+        <v>4875500</v>
       </c>
       <c r="E45" s="3">
-        <v>3999700</v>
+        <v>4718400</v>
       </c>
       <c r="F45" s="3">
-        <v>3358800</v>
+        <v>4044100</v>
       </c>
       <c r="G45" s="3">
-        <v>6636700</v>
+        <v>4646400</v>
       </c>
       <c r="H45" s="3">
-        <v>4217500</v>
+        <v>378500</v>
       </c>
       <c r="I45" s="3">
-        <v>3616000</v>
+        <v>84700</v>
       </c>
       <c r="J45" s="3">
-        <v>3668900</v>
+        <v>348200</v>
       </c>
       <c r="K45" s="3">
         <v>3544300</v>
@@ -1915,25 +1915,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>48115300</v>
+        <v>44803800</v>
       </c>
       <c r="E46" s="3">
-        <v>40630000</v>
+        <v>43047900</v>
       </c>
       <c r="F46" s="3">
-        <v>39300000</v>
+        <v>44652900</v>
       </c>
       <c r="G46" s="3">
-        <v>33476600</v>
+        <v>42631600</v>
       </c>
       <c r="H46" s="3">
-        <v>40719500</v>
+        <v>53299600</v>
       </c>
       <c r="I46" s="3">
-        <v>37250900</v>
+        <v>47347800</v>
       </c>
       <c r="J46" s="3">
-        <v>36750300</v>
+        <v>48736800</v>
       </c>
       <c r="K46" s="3">
         <v>29357600</v>
@@ -1951,25 +1951,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>143852000</v>
+        <v>2987900</v>
       </c>
       <c r="E47" s="3">
-        <v>137707000</v>
+        <v>2661000</v>
       </c>
       <c r="F47" s="3">
-        <v>137810000</v>
+        <v>2186400</v>
       </c>
       <c r="G47" s="3">
-        <v>230618000</v>
+        <v>2129500</v>
       </c>
       <c r="H47" s="3">
-        <v>90412300</v>
+        <v>109708000</v>
       </c>
       <c r="I47" s="3">
-        <v>83245000</v>
+        <v>98300200</v>
       </c>
       <c r="J47" s="3">
-        <v>76368000</v>
+        <v>101296700</v>
       </c>
       <c r="K47" s="3">
         <v>68153500</v>
@@ -1987,25 +1987,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14384800</v>
+        <v>13394800</v>
       </c>
       <c r="E48" s="3">
-        <v>25885600</v>
+        <v>13713000</v>
       </c>
       <c r="F48" s="3">
-        <v>10839200</v>
+        <v>12431000</v>
       </c>
       <c r="G48" s="3">
-        <v>7733000</v>
+        <v>12193400</v>
       </c>
       <c r="H48" s="3">
-        <v>9238900</v>
+        <v>12093200</v>
       </c>
       <c r="I48" s="3">
-        <v>5517100</v>
+        <v>7012500</v>
       </c>
       <c r="J48" s="3">
-        <v>5250200</v>
+        <v>6962700</v>
       </c>
       <c r="K48" s="3">
         <v>5110300</v>
@@ -2023,25 +2023,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>28618800</v>
+        <v>23063700</v>
       </c>
       <c r="E49" s="3">
-        <v>48291900</v>
+        <v>21191500</v>
       </c>
       <c r="F49" s="3">
-        <v>19489800</v>
+        <v>18659600</v>
       </c>
       <c r="G49" s="3">
-        <v>37222500</v>
+        <v>16043600</v>
       </c>
       <c r="H49" s="3">
-        <v>12000400</v>
+        <v>15143700</v>
       </c>
       <c r="I49" s="3">
-        <v>11974300</v>
+        <v>14766900</v>
       </c>
       <c r="J49" s="3">
-        <v>7509400</v>
+        <v>9890600</v>
       </c>
       <c r="K49" s="3">
         <v>7459300</v>
@@ -2131,25 +2131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7192000</v>
+        <v>12621900</v>
       </c>
       <c r="E52" s="3">
-        <v>10957700</v>
+        <v>13511400</v>
       </c>
       <c r="F52" s="3">
-        <v>8975600</v>
+        <v>12449600</v>
       </c>
       <c r="G52" s="3">
-        <v>14738500</v>
+        <v>11639300</v>
       </c>
       <c r="H52" s="3">
-        <v>11208200</v>
+        <v>15768000</v>
       </c>
       <c r="I52" s="3">
-        <v>10981900</v>
+        <v>14267700</v>
       </c>
       <c r="J52" s="3">
-        <v>9487400</v>
+        <v>6126400</v>
       </c>
       <c r="K52" s="3">
         <v>8951500</v>
@@ -2203,25 +2203,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>242163000</v>
+        <v>225496600</v>
       </c>
       <c r="E54" s="3">
-        <v>221194000</v>
+        <v>234357600</v>
       </c>
       <c r="F54" s="3">
-        <v>216415000</v>
+        <v>241447700</v>
       </c>
       <c r="G54" s="3">
-        <v>195306000</v>
+        <v>248716900</v>
       </c>
       <c r="H54" s="3">
-        <v>163579000</v>
+        <v>214116300</v>
       </c>
       <c r="I54" s="3">
-        <v>148969000</v>
+        <v>189347400</v>
       </c>
       <c r="J54" s="3">
-        <v>135365000</v>
+        <v>179516400</v>
       </c>
       <c r="K54" s="3">
         <v>119032000</v>
@@ -2271,25 +2271,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>14660800</v>
+        <v>13651800</v>
       </c>
       <c r="E57" s="3">
-        <v>13249300</v>
+        <v>14037800</v>
       </c>
       <c r="F57" s="3">
-        <v>13087000</v>
+        <v>15009800</v>
       </c>
       <c r="G57" s="3">
-        <v>28066100</v>
+        <v>14435600</v>
       </c>
       <c r="H57" s="3">
-        <v>14278100</v>
+        <v>18689300</v>
       </c>
       <c r="I57" s="3">
-        <v>15514700</v>
+        <v>19720000</v>
       </c>
       <c r="J57" s="3">
-        <v>14079200</v>
+        <v>18671300</v>
       </c>
       <c r="K57" s="3">
         <v>13039600</v>
@@ -2307,25 +2307,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14415200</v>
+        <v>13423100</v>
       </c>
       <c r="E58" s="3">
-        <v>14930400</v>
+        <v>15818900</v>
       </c>
       <c r="F58" s="3">
-        <v>15250500</v>
+        <v>17490300</v>
       </c>
       <c r="G58" s="3">
-        <v>10925800</v>
+        <v>12729300</v>
       </c>
       <c r="H58" s="3">
-        <v>5963900</v>
+        <v>8450700</v>
       </c>
       <c r="I58" s="3">
-        <v>5616700</v>
+        <v>7143400</v>
       </c>
       <c r="J58" s="3">
-        <v>5123500</v>
+        <v>6798900</v>
       </c>
       <c r="K58" s="3">
         <v>3491900</v>
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>43287500</v>
+        <v>15461900</v>
       </c>
       <c r="E59" s="3">
-        <v>37981000</v>
+        <v>15747500</v>
       </c>
       <c r="F59" s="3">
-        <v>33859500</v>
+        <v>14544400</v>
       </c>
       <c r="G59" s="3">
-        <v>40579800</v>
+        <v>15023900</v>
       </c>
       <c r="H59" s="3">
-        <v>24065100</v>
+        <v>7960100</v>
       </c>
       <c r="I59" s="3">
-        <v>22035300</v>
+        <v>7049100</v>
       </c>
       <c r="J59" s="3">
-        <v>20703200</v>
+        <v>7120500</v>
       </c>
       <c r="K59" s="3">
         <v>18663100</v>
@@ -2379,25 +2379,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>72363500</v>
+        <v>67383200</v>
       </c>
       <c r="E60" s="3">
-        <v>66160700</v>
+        <v>70098000</v>
       </c>
       <c r="F60" s="3">
-        <v>62197100</v>
+        <v>71376400</v>
       </c>
       <c r="G60" s="3">
-        <v>52210600</v>
+        <v>66488900</v>
       </c>
       <c r="H60" s="3">
-        <v>44307100</v>
+        <v>57995600</v>
       </c>
       <c r="I60" s="3">
-        <v>43166700</v>
+        <v>54867000</v>
       </c>
       <c r="J60" s="3">
-        <v>39905800</v>
+        <v>52921600</v>
       </c>
       <c r="K60" s="3">
         <v>35194500</v>
@@ -2415,25 +2415,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14612600</v>
+        <v>8998400</v>
       </c>
       <c r="E61" s="3">
-        <v>12550600</v>
+        <v>8346800</v>
       </c>
       <c r="F61" s="3">
-        <v>8545900</v>
+        <v>5969800</v>
       </c>
       <c r="G61" s="3">
-        <v>7480800</v>
+        <v>6390600</v>
       </c>
       <c r="H61" s="3">
-        <v>4508300</v>
+        <v>8987700</v>
       </c>
       <c r="I61" s="3">
-        <v>4035400</v>
+        <v>5236700</v>
       </c>
       <c r="J61" s="3">
-        <v>4426500</v>
+        <v>6001100</v>
       </c>
       <c r="K61" s="3">
         <v>4593100</v>
@@ -2451,25 +2451,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100119000</v>
+        <v>4595900</v>
       </c>
       <c r="E62" s="3">
-        <v>183349000</v>
+        <v>4811200</v>
       </c>
       <c r="F62" s="3">
-        <v>94571400</v>
+        <v>4544100</v>
       </c>
       <c r="G62" s="3">
-        <v>96430000</v>
+        <v>3000400</v>
       </c>
       <c r="H62" s="3">
-        <v>80703100</v>
+        <v>2527700</v>
       </c>
       <c r="I62" s="3">
-        <v>70204100</v>
+        <v>2431800</v>
       </c>
       <c r="J62" s="3">
-        <v>65072800</v>
+        <v>2489900</v>
       </c>
       <c r="K62" s="3">
         <v>58030600</v>
@@ -2595,25 +2595,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>188294000</v>
+        <v>173861100</v>
       </c>
       <c r="E66" s="3">
-        <v>174345000</v>
+        <v>183923000</v>
       </c>
       <c r="F66" s="3">
-        <v>165689000</v>
+        <v>194980600</v>
       </c>
       <c r="G66" s="3">
-        <v>147875000</v>
+        <v>187891700</v>
       </c>
       <c r="H66" s="3">
-        <v>134290000</v>
+        <v>169532500</v>
       </c>
       <c r="I66" s="3">
-        <v>122370000</v>
+        <v>149229300</v>
       </c>
       <c r="J66" s="3">
-        <v>114297000</v>
+        <v>145088900</v>
       </c>
       <c r="K66" s="3">
         <v>102201000</v>
@@ -2791,25 +2791,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>42617100</v>
+        <v>39684000</v>
       </c>
       <c r="E72" s="3">
-        <v>36156300</v>
+        <v>38308000</v>
       </c>
       <c r="F72" s="3">
-        <v>26701400</v>
+        <v>33958600</v>
       </c>
       <c r="G72" s="3">
-        <v>20693000</v>
+        <v>26352000</v>
       </c>
       <c r="H72" s="3">
-        <v>19658900</v>
+        <v>25732400</v>
       </c>
       <c r="I72" s="3">
-        <v>16476200</v>
+        <v>20942000</v>
       </c>
       <c r="J72" s="3">
-        <v>10226700</v>
+        <v>13562300</v>
       </c>
       <c r="K72" s="3">
         <v>6634600</v>
@@ -2935,25 +2935,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>53869000</v>
+        <v>50161500</v>
       </c>
       <c r="E76" s="3">
-        <v>46849600</v>
+        <v>49637700</v>
       </c>
       <c r="F76" s="3">
-        <v>50725700</v>
+        <v>46037400</v>
       </c>
       <c r="G76" s="3">
-        <v>47430400</v>
+        <v>60401500</v>
       </c>
       <c r="H76" s="3">
-        <v>29289700</v>
+        <v>38338600</v>
       </c>
       <c r="I76" s="3">
-        <v>26599300</v>
+        <v>33809000</v>
       </c>
       <c r="J76" s="3">
-        <v>21068300</v>
+        <v>27940000</v>
       </c>
       <c r="K76" s="3">
         <v>16831400</v>
@@ -3018,7 +3018,7 @@
         <v>45016</v>
       </c>
       <c r="F80" s="2">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="G80" s="2">
         <v>44286</v>
@@ -3048,25 +3048,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6891100</v>
+        <v>6416800</v>
       </c>
       <c r="E81" s="3">
-        <v>7137500</v>
+        <v>7562200</v>
       </c>
       <c r="F81" s="3">
-        <v>6263500</v>
+        <v>7183300</v>
       </c>
       <c r="G81" s="3">
-        <v>7171100</v>
+        <v>9309400</v>
       </c>
       <c r="H81" s="3">
-        <v>4133600</v>
+        <v>5410600</v>
       </c>
       <c r="I81" s="3">
-        <v>6505500</v>
+        <v>8268800</v>
       </c>
       <c r="J81" s="3">
-        <v>3484600</v>
+        <v>4621200</v>
       </c>
       <c r="K81" s="3">
         <v>494000</v>
@@ -3100,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8129400</v>
+        <v>2747200</v>
       </c>
       <c r="E83" s="3">
-        <v>7132600</v>
+        <v>2667200</v>
       </c>
       <c r="F83" s="3">
-        <v>5930200</v>
+        <v>6744700</v>
       </c>
       <c r="G83" s="3">
-        <v>4880300</v>
+        <v>6149300</v>
       </c>
       <c r="H83" s="3">
-        <v>2958200</v>
+        <v>2780100</v>
       </c>
       <c r="I83" s="3">
-        <v>2655600</v>
+        <v>2386900</v>
       </c>
       <c r="J83" s="3">
-        <v>2566300</v>
+        <v>1599100</v>
       </c>
       <c r="K83" s="3">
         <v>2204300</v>
@@ -3316,25 +3316,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>9749800</v>
+        <v>9078800</v>
       </c>
       <c r="E89" s="3">
-        <v>2234300</v>
+        <v>2367300</v>
       </c>
       <c r="F89" s="3">
-        <v>8758900</v>
+        <v>10045200</v>
       </c>
       <c r="G89" s="3">
-        <v>8095500</v>
+        <v>10309500</v>
       </c>
       <c r="H89" s="3">
-        <v>9562300</v>
+        <v>12543900</v>
       </c>
       <c r="I89" s="3">
-        <v>8910500</v>
+        <v>11359400</v>
       </c>
       <c r="J89" s="3">
-        <v>8856300</v>
+        <v>11807100</v>
       </c>
       <c r="K89" s="3">
         <v>5454400</v>
@@ -3368,25 +3368,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4430000</v>
+        <v>-4125100</v>
       </c>
       <c r="E91" s="3">
-        <v>-4356800</v>
+        <v>-4616100</v>
       </c>
       <c r="F91" s="3">
-        <v>-3131800</v>
+        <v>-3591700</v>
       </c>
       <c r="G91" s="3">
-        <v>-7030200</v>
+        <v>-4321300</v>
       </c>
       <c r="H91" s="3">
-        <v>-3122300</v>
+        <v>-4086900</v>
       </c>
       <c r="I91" s="3">
-        <v>-2219800</v>
+        <v>-2821400</v>
       </c>
       <c r="J91" s="3">
-        <v>-1867200</v>
+        <v>-2476200</v>
       </c>
       <c r="K91" s="3">
         <v>-2247900</v>
@@ -3476,25 +3476,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5814100</v>
+        <v>-5413900</v>
       </c>
       <c r="E94" s="3">
-        <v>-7473900</v>
+        <v>-7918700</v>
       </c>
       <c r="F94" s="3">
-        <v>-5174300</v>
+        <v>-5934300</v>
       </c>
       <c r="G94" s="3">
-        <v>-4003800</v>
+        <v>-5098700</v>
       </c>
       <c r="H94" s="3">
-        <v>-9601200</v>
+        <v>-12567400</v>
       </c>
       <c r="I94" s="3">
-        <v>-9282900</v>
+        <v>-11799000</v>
       </c>
       <c r="J94" s="3">
-        <v>-5843800</v>
+        <v>-7749800</v>
       </c>
       <c r="K94" s="3">
         <v>-8451800</v>
@@ -3528,25 +3528,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-700200</v>
+        <v>652000</v>
       </c>
       <c r="E96" s="3">
-        <v>-614600</v>
+        <v>651200</v>
       </c>
       <c r="F96" s="3">
-        <v>-527800</v>
+        <v>605300</v>
       </c>
       <c r="G96" s="3">
-        <v>-435100</v>
+        <v>554100</v>
       </c>
       <c r="H96" s="3">
-        <v>-352000</v>
+        <v>460700</v>
       </c>
       <c r="I96" s="3">
-        <v>-270300</v>
+        <v>343500</v>
       </c>
       <c r="J96" s="3">
-        <v>-202300</v>
+        <v>268300</v>
       </c>
       <c r="K96" s="3">
         <v>-170500</v>
@@ -3672,25 +3672,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1496000</v>
+        <v>-1393100</v>
       </c>
       <c r="E100" s="3">
-        <v>598500</v>
+        <v>634100</v>
       </c>
       <c r="F100" s="3">
-        <v>-2389700</v>
+        <v>-2740700</v>
       </c>
       <c r="G100" s="3">
-        <v>-2403600</v>
+        <v>-3060900</v>
       </c>
       <c r="H100" s="3">
-        <v>466200</v>
+        <v>610200</v>
       </c>
       <c r="I100" s="3">
-        <v>-872500</v>
+        <v>-1109000</v>
       </c>
       <c r="J100" s="3">
-        <v>1749800</v>
+        <v>2320600</v>
       </c>
       <c r="K100" s="3">
         <v>3048500</v>
@@ -3708,25 +3708,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>586400</v>
+        <v>546100</v>
       </c>
       <c r="E101" s="3">
-        <v>603100</v>
+        <v>638900</v>
       </c>
       <c r="F101" s="3">
-        <v>670000</v>
+        <v>768400</v>
       </c>
       <c r="G101" s="3">
-        <v>260500</v>
+        <v>331700</v>
       </c>
       <c r="H101" s="3">
-        <v>-153700</v>
+        <v>-201100</v>
       </c>
       <c r="I101" s="3">
-        <v>372500</v>
+        <v>473500</v>
       </c>
       <c r="J101" s="3">
-        <v>-376600</v>
+        <v>-499400</v>
       </c>
       <c r="K101" s="3">
         <v>-209400</v>
@@ -3744,25 +3744,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3026100</v>
+        <v>2817800</v>
       </c>
       <c r="E102" s="3">
-        <v>-4038000</v>
+        <v>-4278300</v>
       </c>
       <c r="F102" s="3">
-        <v>1864800</v>
+        <v>2138700</v>
       </c>
       <c r="G102" s="3">
-        <v>1948700</v>
+        <v>2481600</v>
       </c>
       <c r="H102" s="3">
-        <v>273700</v>
+        <v>385500</v>
       </c>
       <c r="I102" s="3">
-        <v>-872300</v>
+        <v>-1075000</v>
       </c>
       <c r="J102" s="3">
-        <v>4385700</v>
+        <v>5878400</v>
       </c>
       <c r="K102" s="3">
         <v>-158200</v>

--- a/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
   <si>
     <t>SONY</t>
   </si>
@@ -656,171 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44652</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>86525800</v>
+      </c>
+      <c r="E8" s="3">
         <v>86084900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>82555000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>80788200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>81363000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>76763300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>78203100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>80360300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>51245900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>59577000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>70081500</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>56794100</v>
+      </c>
+      <c r="E9" s="3">
         <v>53379400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>53865200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>47600800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>45804000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>44173700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>46482700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>48851400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35153800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>41207500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>48568200</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>24445300</v>
+      </c>
+      <c r="E10" s="3">
         <v>22085200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>24442900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21999000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21981300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>21713900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>21675000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>21695600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16092100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18369400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>21513200</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,44 +847,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>4910700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5534300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5035200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4930900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4640200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4342600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4317300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3015900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3441100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3960600</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,81 +922,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-571000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>116900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-434000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>381200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1496200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>161900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>755300</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7699500</v>
+      </c>
+      <c r="E15" s="3">
         <v>2408300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2321600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6744700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6149300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3810000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3374600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2761500</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1017,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>77076400</v>
+      </c>
+      <c r="E17" s="3">
         <v>78261400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>72859600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>71730200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>72710400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>68845400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>70537400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>73392800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>49300100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>57414600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>69496700</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9449400</v>
+      </c>
+      <c r="E18" s="3">
         <v>7823500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>9695500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9057900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8652500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7917900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7665700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6967500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1945900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2162300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>584700</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1080,188 +1112,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-12700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-79800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>17800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>183100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>114900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>282100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-151900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>261600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-44500</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17096400</v>
+      </c>
+      <c r="E21" s="3">
         <v>10239900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>12029700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>15882500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14784000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11544900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10925400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9446900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4008100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5314800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3600600</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>483900</v>
+      </c>
+      <c r="E22" s="3">
         <v>271000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>198600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>118900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>128500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>103100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>112500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>127700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>98000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>185900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>201300</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9841400</v>
+      </c>
+      <c r="E23" s="3">
         <v>8387600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9587400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9099500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>9023300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7429700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>9129600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6582100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1695900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2238100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>338900</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2095800</v>
+      </c>
+      <c r="E24" s="3">
         <v>1905200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1976300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1865500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-415300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1646700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>407000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1429000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>836200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>696700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>756900</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1295,81 +1343,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7745600</v>
+      </c>
+      <c r="E26" s="3">
         <v>6482400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7611100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7234000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9438600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5783000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8722600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5153000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>859800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1541400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-418000</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7623500</v>
+      </c>
+      <c r="E27" s="3">
         <v>6416800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>7562200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7183300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>9309400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5410600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8268900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4621200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>494000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1086300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1074600</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1403,9 +1460,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1439,9 +1499,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1538,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1577,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E32" s="3">
         <v>8100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>12700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>79800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-17800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-183100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-114900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-282100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>151900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-261600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>44500</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7623500</v>
+      </c>
+      <c r="E33" s="3">
         <v>6416800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>7562200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7183300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>9309400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5410600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8268800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4621200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>494000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1086300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1074600</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1694,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7623500</v>
+      </c>
+      <c r="E35" s="3">
         <v>6416800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>7562200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7183300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>9309400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5410600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8268800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4621200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>494000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1086300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1074600</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44652</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +1797,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,44 +1814,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11784300</v>
+      </c>
+      <c r="E41" s="3">
         <v>6567000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5449400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9449600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11661600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8943300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8667800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14936500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6471400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7229500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8098500</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1783,278 +1872,302 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>195700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11078800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7086700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6956000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7990300</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12976400</v>
+      </c>
+      <c r="E43" s="3">
         <v>14268600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13322000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13204500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12346300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11068800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11636300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11331700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7936000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7788400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9654700</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8753200</v>
+      </c>
+      <c r="E44" s="3">
         <v>10040300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11043400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7116800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5756500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5482900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5895500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6524500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4319200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5021100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5676100</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4331800</v>
+      </c>
+      <c r="E45" s="3">
         <v>4875500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4718400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4044100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4646400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>378500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>84700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>348200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3544300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3850800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4388500</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49783600</v>
+      </c>
+      <c r="E46" s="3">
         <v>44803800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43047900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44652900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>42631600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>53299600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>47347800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>48736800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29357600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>30845900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35808100</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2300800</v>
+      </c>
+      <c r="E47" s="3">
         <v>2987900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2661000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2186400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2129500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>109708000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>98300200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>101296700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>68153500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>67870500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>72772400</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13591800</v>
+      </c>
+      <c r="E48" s="3">
         <v>13394800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13713000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12431000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12193400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12093200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7012500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6962700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5110300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6033000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6306100</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>29576200</v>
+      </c>
+      <c r="E49" s="3">
         <v>23063700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>21191500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18659600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>16043600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15143700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14766900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9890600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7459300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8982000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10266800</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2201,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,45 +2240,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11556500</v>
+      </c>
+      <c r="E52" s="3">
         <v>12621900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13511400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12449600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11639300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15768000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14267700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6126400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8951500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8817900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9913400</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2318,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>235683800</v>
+      </c>
+      <c r="E54" s="3">
         <v>225496600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>234357600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>241447700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>248716900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>214116300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>189347400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>179516400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119032000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>122549000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>135067000</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2377,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,224 +2394,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14024500</v>
+      </c>
+      <c r="E57" s="3">
         <v>13651800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14037800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15009800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14435600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18689300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>19720000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18671300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13039600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14097900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17028600</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14233300</v>
+      </c>
+      <c r="E58" s="3">
         <v>13423100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>15818900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17490300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12729300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8450700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7143400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6798900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3491900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2476500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1889600</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15996600</v>
+      </c>
+      <c r="E59" s="3">
         <v>15461900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15747500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14544400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15023900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7960100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7049100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7120500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18663100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18931600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21561700</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>71378500</v>
+      </c>
+      <c r="E60" s="3">
         <v>67383200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70098000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>71376400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>66488900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>57995600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>54867000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52921600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35194500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35506000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>40479900</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9192700</v>
+      </c>
+      <c r="E61" s="3">
         <v>8998400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8346800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5969800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6390600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>8987700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5236700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6001100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4593100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4091000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6074100</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6183200</v>
+      </c>
+      <c r="E62" s="3">
         <v>4595900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4811200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4544100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3000400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2527700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2431800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2489900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>58030600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>59933000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63488300</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +2664,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,9 +2703,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +2742,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>178854000</v>
+      </c>
+      <c r="E66" s="3">
         <v>173861100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>183923000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>194980600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>187891700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>169532500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>149229300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>145088900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>102201000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>104444000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>115302000</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +2801,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +2837,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,9 +2876,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2748,9 +2915,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,45 +2954,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>44596000</v>
+      </c>
+      <c r="E72" s="3">
         <v>39684000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>38308000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>33958600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26352000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25732400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20942000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13562300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6634600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6882000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6941400</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3032,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3071,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3110,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>54623400</v>
+      </c>
+      <c r="E76" s="3">
         <v>50161500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49637700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46037400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>60401500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>38338600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>33809000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27940000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16831400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>18105500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19764700</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3188,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44652</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7623500</v>
+      </c>
+      <c r="E81" s="3">
         <v>6416800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>7562200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7183300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>9309400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5410600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8268800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4621200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>494000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1086300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1074600</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,44 +3291,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7699500</v>
+      </c>
+      <c r="E83" s="3">
         <v>2747200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2667200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6744700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6149300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2780100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2386900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1599100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2204300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2918600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3024900</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3366,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +3405,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +3444,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +3483,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +3522,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15503900</v>
+      </c>
+      <c r="E89" s="3">
         <v>9078800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2367300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10045200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10309500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12543900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11359400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>11807100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5454400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5505800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6437100</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,44 +3581,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4324100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4125100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4616100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3591700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4321300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4086900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2821400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2476200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2247900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2759300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1841800</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +3656,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +3695,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6211200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5413900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7918700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-5934300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5098700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12567400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11799000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7749800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8451800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7573500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5456100</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,44 +3754,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>769600</v>
+      </c>
+      <c r="E96" s="3">
         <v>652000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>651200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>605300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>554100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>460700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>343500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>268300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-170500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-93700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-112300</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +3829,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +3868,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,115 +3907,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1991600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1393100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>634100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2740700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3060900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>610200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1109000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2320600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3048500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2793900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2245100</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-130000</v>
+      </c>
+      <c r="E101" s="3">
         <v>546100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>638900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>768400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>331700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-201100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>473500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-499400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-209400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-474900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>436200</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7171000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2817800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4278300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2138700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2481600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>385500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1075000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5878400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-158200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>251400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-827900</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SONY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
   <si>
     <t>SONY</t>
   </si>
@@ -759,13 +759,13 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>56794100</v>
+        <v>56693300</v>
       </c>
       <c r="E9" s="3">
         <v>53379400</v>
       </c>
       <c r="F9" s="3">
-        <v>53865200</v>
+        <v>53972100</v>
       </c>
       <c r="G9" s="3">
         <v>47600800</v>
@@ -798,13 +798,13 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>24445300</v>
+        <v>24559300</v>
       </c>
       <c r="E10" s="3">
-        <v>22085200</v>
+        <v>22084800</v>
       </c>
       <c r="F10" s="3">
-        <v>24442900</v>
+        <v>24336100</v>
       </c>
       <c r="G10" s="3">
         <v>21999000</v>
@@ -853,8 +853,8 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>4905400</v>
       </c>
       <c r="E12" s="3">
         <v>4910700</v>
@@ -931,14 +931,14 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-434000</v>
       </c>
       <c r="E14" s="3">
-        <v>-571000</v>
+        <v>-577200</v>
       </c>
       <c r="F14" s="3">
-        <v>116900</v>
+        <v>-800</v>
       </c>
       <c r="G14" s="3">
         <v>-1000</v>
@@ -971,13 +971,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>7699500</v>
+        <v>2573300</v>
       </c>
       <c r="E15" s="3">
         <v>2408300</v>
       </c>
       <c r="F15" s="3">
-        <v>2321600</v>
+        <v>7521800</v>
       </c>
       <c r="G15" s="3">
         <v>6744700</v>
@@ -1024,13 +1024,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>77076400</v>
+        <v>76991100</v>
       </c>
       <c r="E17" s="3">
-        <v>78261400</v>
+        <v>78268000</v>
       </c>
       <c r="F17" s="3">
-        <v>72859600</v>
+        <v>72977300</v>
       </c>
       <c r="G17" s="3">
         <v>71730200</v>
@@ -1063,13 +1063,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>9449400</v>
+        <v>9534700</v>
       </c>
       <c r="E18" s="3">
-        <v>7823500</v>
+        <v>7816900</v>
       </c>
       <c r="F18" s="3">
-        <v>9695500</v>
+        <v>9577700</v>
       </c>
       <c r="G18" s="3">
         <v>9057900</v>
@@ -1119,10 +1119,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>52500</v>
+        <v>203600</v>
       </c>
       <c r="E20" s="3">
-        <v>-8100</v>
+        <v>-8500</v>
       </c>
       <c r="F20" s="3">
         <v>-12700</v>
@@ -1158,13 +1158,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17096400</v>
+        <v>11904300</v>
       </c>
       <c r="E21" s="3">
-        <v>10239900</v>
+        <v>10233700</v>
       </c>
       <c r="F21" s="3">
-        <v>12029700</v>
+        <v>17112200</v>
       </c>
       <c r="G21" s="3">
         <v>15882500</v>
@@ -1197,7 +1197,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>483900</v>
+        <v>273000</v>
       </c>
       <c r="E22" s="3">
         <v>271000</v>
@@ -1587,10 +1587,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-52500</v>
+        <v>-203600</v>
       </c>
       <c r="E32" s="3">
-        <v>8100</v>
+        <v>8500</v>
       </c>
       <c r="F32" s="3">
         <v>12700</v>
@@ -2055,7 +2055,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2300800</v>
+        <v>2468700</v>
       </c>
       <c r="E47" s="3">
         <v>2987900</v>
@@ -2133,7 +2133,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>29576200</v>
+        <v>25743300</v>
       </c>
       <c r="E49" s="3">
         <v>23063700</v>
@@ -2250,7 +2250,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11556500</v>
+        <v>15149200</v>
       </c>
       <c r="E52" s="3">
         <v>12621900</v>
@@ -2557,7 +2557,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9192700</v>
+        <v>9291700</v>
       </c>
       <c r="E61" s="3">
         <v>8998400</v>
@@ -2596,7 +2596,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6183200</v>
+        <v>5803400</v>
       </c>
       <c r="E62" s="3">
         <v>4595900</v>
@@ -2752,7 +2752,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>178854000</v>
+        <v>178573100</v>
       </c>
       <c r="E66" s="3">
         <v>173861100</v>
@@ -3298,13 +3298,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7699500</v>
+        <v>2996600</v>
       </c>
       <c r="E83" s="3">
         <v>2747200</v>
       </c>
       <c r="F83" s="3">
-        <v>2667200</v>
+        <v>7521800</v>
       </c>
       <c r="G83" s="3">
         <v>6744700</v>
